--- a/docs/tcm-import-resource-viewer.xlsx
+++ b/docs/tcm-import-resource-viewer.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta" sheetId="1" r:id="R0e347c303cc944b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Features" sheetId="2" r:id="Raf484fb7aa6d46e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AcceptanceCriteria" sheetId="3" r:id="Rf2e002184d6e4ea0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TestCases" sheetId="4" r:id="R76210caebbd544ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steps" sheetId="5" r:id="R585de4d9a5fb42a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DatasetSchema" sheetId="6" r:id="Rd04438c7957e484b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ParameterSets" sheetId="7" r:id="Rd916527d4eeb4157"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AutomationLinks" sheetId="8" r:id="Rfe96e32f59aa448c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CrossFeatures" sheetId="9" r:id="Rbc955ab90e23417e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta" sheetId="1" r:id="R90689e4a57e745c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Features" sheetId="2" r:id="R0fd3e77a9bd44388"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AcceptanceCriteria" sheetId="3" r:id="Rddd026c1545b4c29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TestCases" sheetId="4" r:id="Rf48fda9a7aef4527"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steps" sheetId="5" r:id="R18f4f5c6acb2421f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DatasetSchema" sheetId="6" r:id="Rbcc81bf355d5437d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ParameterSets" sheetId="7" r:id="R7eac9eace6e84091"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AutomationLinks" sheetId="8" r:id="R0d562c6624ba4304"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CrossFeatures" sheetId="9" r:id="Rae26af7b66d5422d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1051,6 +1051,20 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>REQ-RVW-BOM</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>AC-15</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>Якщо на момент переміщення не існувало жодної tech map, ресурс залишається атомарним; карта, створена пізніше, на нього не впливає.</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2813,6 +2827,104 @@
       </x:c>
       <x:c r="Q35" t="str"/>
     </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>TC-RVW-BOM-035</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>REQ-RVW-BOM</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>AC-15</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>BOM — до першої tech map ресурс атомарний</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>Мета: Якщо на момент переміщення не існувало жодної tech map, пізніше створена карта не змінює історичний склад.</x:v>
+      </x:c>
+      <x:c r="F36" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="G36" t="str">
+        <x:v>CRITICAL</x:v>
+      </x:c>
+      <x:c r="H36" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="I36" t="str">
+        <x:v>FUNCTIONAL</x:v>
+      </x:c>
+      <x:c r="J36" t="str">
+        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging. @Admin підготував техкарти PRODUCTION + stock на OWNER_1 storage; receiver = UNIT storage.</x:v>
+      </x:c>
+      <x:c r="K36" t="str">
+        <x:v>Component відсутній; Product лишається атомарним, isProduct=false</x:v>
+      </x:c>
+      <x:c r="L36" t="str">
+        <x:v>resource-viewer,api</x:v>
+      </x:c>
+      <x:c r="M36" t="str">
+        <x:v>QA</x:v>
+      </x:c>
+      <x:c r="N36"/>
+      <x:c r="O36" t="str">
+        <x:v>ResourceViewer</x:v>
+      </x:c>
+      <x:c r="P36" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="Q36"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>TC-RVW-BOM-036</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>REQ-RVW-BOM</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>AC-15</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>BOM — зовнішня партія до першої tech map атомарна</x:v>
+      </x:c>
+      <x:c r="E37" t="str">
+        <x:v>Мета: Зовнішньо отримана партія, переміщена до появи першої tech map, лишається атомарною; пізніше створена карта не змінює історичний склад.</x:v>
+      </x:c>
+      <x:c r="F37" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="G37" t="str">
+        <x:v>CRITICAL</x:v>
+      </x:c>
+      <x:c r="H37" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="I37" t="str">
+        <x:v>FUNCTIONAL</x:v>
+      </x:c>
+      <x:c r="J37" t="str">
+        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging. @Admin підготував техкарти PRODUCTION + stock на OWNER_1 storage; receiver = UNIT storage.</x:v>
+      </x:c>
+      <x:c r="K37" t="str">
+        <x:v>Один атомарний рядок Product, isProduct=false</x:v>
+      </x:c>
+      <x:c r="L37" t="str">
+        <x:v>resource-viewer,api</x:v>
+      </x:c>
+      <x:c r="M37" t="str">
+        <x:v>QA</x:v>
+      </x:c>
+      <x:c r="N37"/>
+      <x:c r="O37" t="str">
+        <x:v>ResourceViewer</x:v>
+      </x:c>
+      <x:c r="P37" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="Q37"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3824,6 +3936,104 @@
         <x:v>є product і ingredient рядки для Alcohol</x:v>
       </x:c>
     </x:row>
+    <x:row r="72">
+      <x:c r="A72" t="str">
+        <x:v>TC-RVW-BOM-035</x:v>
+      </x:c>
+      <x:c r="B72" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C72" t="str">
+        <x:v>Створити inventory stock Product і перемістити його до появи tech map</x:v>
+      </x:c>
+      <x:c r="D72" t="str">
+        <x:v>relocationId</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" t="str">
+        <x:v>TC-RVW-BOM-035</x:v>
+      </x:c>
+      <x:c r="B73" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C73" t="str">
+        <x:v>Після переміщення створити tech map Product←Component</x:v>
+      </x:c>
+      <x:c r="D73" t="str">
+        <x:v>Tech map створена пізніше</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" t="str">
+        <x:v>TC-RVW-BOM-035</x:v>
+      </x:c>
+      <x:c r="B74" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C74" t="str">
+        <x:v>GET journal/sum</x:v>
+      </x:c>
+      <x:c r="D74" t="str">
+        <x:v>Component відсутній; Product лишається атомарним, isProduct=false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" t="str">
+        <x:v>TC-RVW-BOM-036</x:v>
+      </x:c>
+      <x:c r="B75" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C75" t="str">
+        <x:v>Отримати Product зовнішньою партією та перемістити її до появи tech map</x:v>
+      </x:c>
+      <x:c r="D75" t="str">
+        <x:v>relocationId; isProduced=false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" t="str">
+        <x:v>TC-RVW-BOM-036</x:v>
+      </x:c>
+      <x:c r="B76" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C76" t="str">
+        <x:v>Після переміщення створити tech map Product←Component</x:v>
+      </x:c>
+      <x:c r="D76" t="str">
+        <x:v>Tech map створена пізніше</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" t="str">
+        <x:v>TC-RVW-BOM-036</x:v>
+      </x:c>
+      <x:c r="B77" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C77" t="str">
+        <x:v>GET journal/sum за Component</x:v>
+      </x:c>
+      <x:c r="D77" t="str">
+        <x:v>Relocation відсутній; Component amount=0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" t="str">
+        <x:v>TC-RVW-BOM-036</x:v>
+      </x:c>
+      <x:c r="B78" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C78" t="str">
+        <x:v>GET journal за Product</x:v>
+      </x:c>
+      <x:c r="D78" t="str">
+        <x:v>Один атомарний рядок Product, isProduct=false</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -4403,6 +4613,34 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>TC-RVW-BOM-035</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>API</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>TC-RVW-BOM-035</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>TC-RVW-BOM-036</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>API</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>TC-RVW-BOM-036</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -4696,6 +4934,22 @@
         <x:v>resource-viewer</x:v>
       </x:c>
     </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>TC-RVW-BOM-035</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>resource-viewer</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>TC-RVW-BOM-036</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>resource-viewer</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/docs/tcm-import-resource-viewer.xlsx
+++ b/docs/tcm-import-resource-viewer.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta" sheetId="1" r:id="R90689e4a57e745c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Features" sheetId="2" r:id="R0fd3e77a9bd44388"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AcceptanceCriteria" sheetId="3" r:id="Rddd026c1545b4c29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TestCases" sheetId="4" r:id="Rf48fda9a7aef4527"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steps" sheetId="5" r:id="R18f4f5c6acb2421f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DatasetSchema" sheetId="6" r:id="Rbcc81bf355d5437d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ParameterSets" sheetId="7" r:id="R7eac9eace6e84091"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AutomationLinks" sheetId="8" r:id="R0d562c6624ba4304"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CrossFeatures" sheetId="9" r:id="Rae26af7b66d5422d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta" sheetId="1" r:id="Rdf6794e3e1054139"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Features" sheetId="2" r:id="Re8a284738cec41e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AcceptanceCriteria" sheetId="3" r:id="Rf226446ce9234b87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TestCases" sheetId="4" r:id="Red723dbdc4f14ebd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steps" sheetId="5" r:id="R98ced061dfdc4d0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DatasetSchema" sheetId="6" r:id="Rbb0e9e1a23ec4995"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ParameterSets" sheetId="7" r:id="Ra6769cf8c5fe4d93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AutomationLinks" sheetId="8" r:id="R6ebb7756d5ef47be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CrossFeatures" sheetId="9" r:id="Rd1663e2dc0ee4c91"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -336,95 +336,65 @@
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">key</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">value</x:t>
-        </x:is>
+      <x:c r="A1" t="str">
+        <x:v>key</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>value</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">formatVersion</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
+      <x:c r="A2" t="str">
+        <x:v>formatVersion</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">exportedAt</x:t>
-        </x:is>
+      <x:c r="A3" t="str">
+        <x:v>exportedAt</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>2026-09-17T10:09:02</x:v>
+        <x:v>2026-09-22T11:50:32</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">projectId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
+      <x:c r="A4" t="str">
+        <x:v>projectId</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">projectName</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ERP Система</x:t>
-        </x:is>
+      <x:c r="A5" t="str">
+        <x:v>projectName</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>ERP Система</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">scope</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PROJECT</x:t>
-        </x:is>
+      <x:c r="A6" t="str">
+        <x:v>scope</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>PROJECT</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">rootFeatureId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
+      <x:c r="A7" t="str">
+        <x:v>rootFeatureId</x:v>
+      </x:c>
+      <x:c r="B7" t="str"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">source</x:t>
-        </x:is>
+      <x:c r="A8" t="str">
+        <x:v>source</x:v>
       </x:c>
       <x:c r="B8" t="str">
-        <x:v>erp-auto-test resource-viewer business rules + tests 2026-09-17</x:v>
+        <x:v>erp-auto-test resource-viewer business rules + tests 2026-09-22</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -437,55 +407,35 @@
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">featureId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">parentFeatureId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">title</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">description</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">module</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">priority</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">status</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">author</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">treeDepth</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">sortOrder</x:t>
-        </x:is>
+      <x:c r="A1" t="str">
+        <x:v>featureId</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>parentFeatureId</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>title</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>description</x:v>
+      </x:c>
+      <x:c r="E1" t="str">
+        <x:v>module</x:v>
+      </x:c>
+      <x:c r="F1" t="str">
+        <x:v>priority</x:v>
+      </x:c>
+      <x:c r="G1" t="str">
+        <x:v>status</x:v>
+      </x:c>
+      <x:c r="H1" t="str">
+        <x:v>author</x:v>
+      </x:c>
+      <x:c r="I1" t="str">
+        <x:v>treeDepth</x:v>
+      </x:c>
+      <x:c r="J1" t="str">
+        <x:v>sortOrder</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -529,7 +479,7 @@
         <x:v>Розрахунок компонентів продукту</x:v>
       </x:c>
       <x:c r="D3" t="str">
-        <x:v>Для переміщеного продукту система визначає фактично використані компоненти за виробничими даними, масштабує їх до кількості переміщення та проходить вкладені рецептури. Якщо виробничих фактів немає і зовнішнє походження продукту не підтверджене, технологічна карта використовується як резервне джерело; без технологічної карти продукт вважається атомарним.</x:v>
+        <x:v>Для переміщеного продукту система визначає фактично використані компоненти за виробничими даними, масштабує їх до кількості переміщення та проходить вкладені рецептури. Кількість без виробничого факту — зокрема підтверджена зовнішня або інвентаризаційна — розкладається за найновішою tech map, що існувала на момент переміщення; без такої карти ресурс вважається атомарним.</x:v>
       </x:c>
       <x:c r="E3" t="str">
         <x:v>RES</x:v>
@@ -561,7 +511,7 @@
         <x:v>Фільтрація, журнал і підсумки</x:v>
       </x:c>
       <x:c r="D4" t="str">
-        <x:v>Фільтри визначають ресурси спостереження, одержувачів, постачальника та період. Один запит повертає сторінку унікальних переміщень і сумарну кількість кожного відстежуваного ресурсу; експорт використовує ті самі критерії.</x:v>
+        <x:v>Фільтри визначають ресурси спостереження, одержувачів, постачальника та період. Category-only пошук згортає пов'язані рівні BOM і повертає унікальні фізичні переміщення; явно вибрані рівні не згортаються. Експорт використовує ті самі критерії.</x:v>
       </x:c>
       <x:c r="E4" t="str">
         <x:v>RES</x:v>
@@ -593,7 +543,7 @@
         <x:v>Сторінка «Відстеження ресурсів»</x:v>
       </x:c>
       <x:c r="D5" t="str">
-        <x:v>Користувач налаштовує фільтри, запускає пошук, бачить журнал і блок «Сумарно переміщено», а також може вивантажити той самий набір даних у Excel.</x:v>
+        <x:v>Користувач налаштовує фільтри, запускає пошук, бачить журнал і блок «Сумарно переміщено», керує напрямком category-only групування та може вивантажити той самий набір даних у Excel.</x:v>
       </x:c>
       <x:c r="E5" t="str">
         <x:v>RES</x:v>
@@ -624,25 +574,17 @@
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">featureId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">acId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">text</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">sortOrder</x:t>
-        </x:is>
+      <x:c r="A1" t="str">
+        <x:v>featureId</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>acId</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>sortOrder</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -653,7 +595,7 @@
         <x:v>AC-01</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>Користувач із правом Resource Viewer має доступ до журналу, підсумків та експорту; селектор джерел містить склади й виробництва, але не підрозділи типу UNIT.</x:v>
+        <x:v>Глобальний Resource Viewer має доступ до журналу, підсумків та експорту без location grants і без залежності від legacy storage types.</x:v>
       </x:c>
       <x:c r="D2" t="str">
         <x:v>0</x:v>
@@ -695,7 +637,7 @@
         <x:v>AC-03</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>Якщо підтверджено, що готовий продукт отримано ззовні, він вважається атомарним: система не розкладає його за внутрішньою технологічною картою та не зараховує її компоненти.</x:v>
+        <x:v>Якщо підтверджено, що готовий продукт отримано ззовні, система розкладає його за алгоритмом інвентаризаційного залишку без партії; для alternative group використовується default-компонент.</x:v>
       </x:c>
       <x:c r="D5" t="str">
         <x:v>2</x:v>
@@ -709,7 +651,7 @@
         <x:v>AC-04</x:v>
       </x:c>
       <x:c r="C6" t="str">
-        <x:v>Якщо переміщення складається з виробленої та отриманої готовою кількості продукту, система розкладає лише частину з підтвердженим власним виробництвом; отримана ззовні частина залишається атомарною.</x:v>
+        <x:v>Якщо переміщення складається з виробленої та отриманої готовою кількості продукту, вироблена частина розкладається за фактичними даними виробництва, а отримана ззовні — за алгоритмом інвентаризаційного залишку без партії.</x:v>
       </x:c>
       <x:c r="D6" t="str">
         <x:v>3</x:v>
@@ -793,7 +735,7 @@
         <x:v>AC-10</x:v>
       </x:c>
       <x:c r="C12" t="str">
-        <x:v>Якщо одну партію створено кількома виробництвами з різними витратами, система використовує зважену середню витрату компонента.</x:v>
+        <x:v>Якщо одну партію створено кількома виробництвами з різними витратами, система використовує дані останнього запису виробництва.</x:v>
       </x:c>
       <x:c r="D12" t="str">
         <x:v>9</x:v>
@@ -807,7 +749,7 @@
         <x:v>AC-11</x:v>
       </x:c>
       <x:c r="C13" t="str">
-        <x:v>Якщо для продукту немає партії та фактичних виробничих даних, а його зовнішнє походження не підтверджене, система визначає склад за останньою активною технологічною картою. Якщо активної карти немає, використовується остання наявна карта; якщо карт немає, продукт вважається атомарним.</x:v>
+        <x:v>Для інвентаризаційного залишку без підтвердженого походження система використовує найновішу активну або архівну tech map, що вже існувала на момент переміщення; alternative group використовує default.</x:v>
       </x:c>
       <x:c r="D13" t="str">
         <x:v>10</x:v>
@@ -821,7 +763,7 @@
         <x:v>AC-12</x:v>
       </x:c>
       <x:c r="C14" t="str">
-        <x:v>Під час fallback система вибирає найновішу карту за версією; якщо версії однакові — за dateTime, а потім за id. Активні карти мають пріоритет над неактивними.</x:v>
+        <x:v>Створення нової карти, деактивація старої або зміна поточної активної карти після переміщення не змінює історичний склад цього переміщення.</x:v>
       </x:c>
       <x:c r="D14" t="str">
         <x:v>11</x:v>
@@ -835,7 +777,7 @@
         <x:v>AC-13</x:v>
       </x:c>
       <x:c r="C15" t="str">
-        <x:v>Циклічне посилання між рецептурами зупиняється без зациклення та повторного підрахунку компонента.</x:v>
+        <x:v>Циклічне посилання A-B-C-A зупиняється як A-B-C без зациклення та повторного підрахунку A.</x:v>
       </x:c>
       <x:c r="D15" t="str">
         <x:v>12</x:v>
@@ -857,30 +799,30 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
-        <x:v>REQ-RVW-FILTER</x:v>
+        <x:v>REQ-RVW-BOM</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>AC-01</x:v>
+        <x:v>AC-15</x:v>
       </x:c>
       <x:c r="C17" t="str">
-        <x:v>Категорія є самостійною ціллю відстеження: ресурси категорії шукаються як прямі переміщення та як компоненти продуктів без обов'язкового вибору окремих ресурсів.</x:v>
+        <x:v>Якщо на момент переміщення не існувало жодної tech map, ресурс залишається атомарним; карта, створена пізніше, на нього не впливає.</x:v>
       </x:c>
       <x:c r="D17" t="str">
-        <x:v>0</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
-        <x:v>REQ-RVW-FILTER</x:v>
+        <x:v>REQ-RVW-BOM</x:v>
       </x:c>
       <x:c r="B18" t="str">
-        <x:v>AC-02</x:v>
+        <x:v>AC-16</x:v>
       </x:c>
       <x:c r="C18" t="str">
-        <x:v>Фільтр постачальника додатково звужує переміщення, відібрані за іншими критеріями.</x:v>
+        <x:v>BOM розкладається лише для переміщень, які перетинають reporting boundary: з дерева TSUK_PARENT_UNITS до зовнішньої структури. Kind і features локацій на рішення не впливають.</x:v>
       </x:c>
       <x:c r="D18" t="str">
-        <x:v>1</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -888,13 +830,13 @@
         <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="B19" t="str">
-        <x:v>AC-03</x:v>
+        <x:v>AC-01</x:v>
       </x:c>
       <x:c r="C19" t="str">
-        <x:v>Початкова й кінцева дати однаково обмежують журнал і підсумки.</x:v>
+        <x:v>Категорія є самостійною ціллю відстеження: ресурси категорії шукаються як прямі переміщення та як компоненти продуктів без обов'язкового вибору окремих ресурсів.</x:v>
       </x:c>
       <x:c r="D19" t="str">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -902,13 +844,13 @@
         <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="B20" t="str">
-        <x:v>AC-04</x:v>
+        <x:v>AC-02</x:v>
       </x:c>
       <x:c r="C20" t="str">
-        <x:v>Без цілі відстеження або без одержувача система повертає успішну порожню відповідь.</x:v>
+        <x:v>Фільтр постачальника додатково звужує переміщення, відібрані за іншими критеріями.</x:v>
       </x:c>
       <x:c r="D20" t="str">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -916,13 +858,13 @@
         <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="B21" t="str">
-        <x:v>AC-05</x:v>
+        <x:v>AC-03</x:v>
       </x:c>
       <x:c r="C21" t="str">
-        <x:v>Журнал підтримує пагінацію, повертає коректну загальну кількість записів і сортується за датою переміщення від нових до старих.</x:v>
+        <x:v>Початкова й кінцева дати однаково обмежують журнал і підсумки.</x:v>
       </x:c>
       <x:c r="D21" t="str">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -930,13 +872,13 @@
         <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="B22" t="str">
-        <x:v>AC-06</x:v>
+        <x:v>AC-04</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>Excel-експорт містить результат за тими самими критеріями, що й журнал; для порожнього обов'язкового контексту тіло експорту порожнє.</x:v>
+        <x:v>Без цілі відстеження або без одержувача система повертає успішну порожню відповідь.</x:v>
       </x:c>
       <x:c r="D22" t="str">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -944,13 +886,13 @@
         <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="B23" t="str">
-        <x:v>AC-07</x:v>
+        <x:v>AC-05</x:v>
       </x:c>
       <x:c r="C23" t="str">
-        <x:v>До результату входять передачі зі складу або виробництва до підрозділу; передачі між підрозділами, зокрема до екіпажу, виключаються.</x:v>
+        <x:v>Журнал підтримує пагінацію, повертає коректну загальну кількість записів і сортується за датою переміщення від нових до старих.</x:v>
       </x:c>
       <x:c r="D23" t="str">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -958,13 +900,13 @@
         <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="B24" t="str">
-        <x:v>AC-08</x:v>
+        <x:v>AC-06</x:v>
       </x:c>
       <x:c r="C24" t="str">
-        <x:v>Підсумки ресурсів сортуються за назвою за зростанням.</x:v>
+        <x:v>Excel-експорт містить результат за тими самими критеріями, що й журнал; для порожнього обов'язкового контексту тіло експорту порожнє.</x:v>
       </x:c>
       <x:c r="D24" t="str">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -972,13 +914,13 @@
         <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="B25" t="str">
-        <x:v>AC-09</x:v>
+        <x:v>AC-07</x:v>
       </x:c>
       <x:c r="C25" t="str">
-        <x:v>До робочого результату входять активні стани CREATED, FINISHED і AUTO_FINISHED; CANCELLED та RETURNED виключаються.</x:v>
+        <x:v>До результату входять переміщення з дочірньої структури TSUK_PARENT_UNITS до структури, яка не належить TSUK_PARENT_UNITS. Перевіряється весь parent-chain; kind, features і legacy storage type відправника та одержувача на рішення не впливають.</x:v>
       </x:c>
       <x:c r="D25" t="str">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -986,13 +928,13 @@
         <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="B26" t="str">
-        <x:v>AC-10</x:v>
+        <x:v>AC-08</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>Одержувачів можна вибирати групами ПМ 414, СБС та Інші; якщо одночасно задано receiverIds, результат є перетином явного списку та вибраної групи.</x:v>
+        <x:v>Підсумки ресурсів сортуються за назвою за зростанням.</x:v>
       </x:c>
       <x:c r="D26" t="str">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1000,69 +942,153 @@
         <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="B27" t="str">
-        <x:v>AC-11</x:v>
+        <x:v>AC-09</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>Кожне фізичне переміщення присутнє в журналі не більше одного разу за relocationId, навіть якщо продукт і один або кілька його компонентів одночасно відповідають критеріям відстеження.</x:v>
+        <x:v>До робочого результату входять активні стани CREATED, FINISHED і AUTO_FINISHED; CANCELLED та RETURNED виключаються.</x:v>
       </x:c>
       <x:c r="D27" t="str">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="str">
-        <x:v>REQ-RVW-UI</x:v>
+        <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="B28" t="str">
-        <x:v>AC-01</x:v>
+        <x:v>AC-10</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>Користувач із правом Resource Viewer бачить пункт «Відстеження ресурсів» і може відкрити журнал.</x:v>
+        <x:v>Одержувачів можна вибирати групами ПМ 414, СБС та Інші; якщо одночасно задано receiverIds, результат є перетином явного списку та вибраної групи.</x:v>
       </x:c>
       <x:c r="D28" t="str">
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="str">
-        <x:v>REQ-RVW-UI</x:v>
+        <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="B29" t="str">
-        <x:v>AC-02</x:v>
+        <x:v>AC-11</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>Після пошуку сторінка показує журнал і блок «Сумарно переміщено»; підсумок у UI відповідає API.</x:v>
+        <x:v>Для пошуку лише за категорією кожне фізичне переміщення присутнє в журналі не більше одного разу за relocationId, навіть якщо продукт і його компоненти належать до вибраної категорії; пов'язані рівні згортаються без подвійного підрахунку.</x:v>
       </x:c>
       <x:c r="D29" t="str">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
-        <x:v>REQ-RVW-UI</x:v>
+        <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="B30" t="str">
-        <x:v>AC-03</x:v>
+        <x:v>AC-12</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>Автодоповнення ресурсів обмежується вибраною категорією та відновлює повний список після її очищення.</x:v>
+        <x:v>Якщо готовий виріб і його напівфабрикат вибрані явно через resourceIds, category-only групування не застосовується: журнал і підсумки показують декомпозицію кожного явно вибраного рівня.</x:v>
       </x:c>
       <x:c r="D30" t="str">
-        <x:v>2</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str">
-        <x:v>REQ-RVW-BOM</x:v>
+        <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="B31" t="str">
-        <x:v>AC-15</x:v>
+        <x:v>AC-13</x:v>
       </x:c>
       <x:c r="C31" t="str">
-        <x:v>Якщо на момент переміщення не існувало жодної tech map, ресурс залишається атомарним; карта, створена пізніше, на нього не впливає.</x:v>
+        <x:v>Для category-only пошуку groupByLowestComponents=true залишає найнижчі пов'язані компоненти, а false — найвищі; groupedFrom пояснює, які рівні було згорнуто.</x:v>
       </x:c>
       <x:c r="D31" t="str">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>REQ-RVW-UI</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>AC-01</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>Користувач із правом Resource Viewer бачить пункт «Відстеження ресурсів» і може відкрити журнал.</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>REQ-RVW-UI</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>AC-02</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>Після пошуку сторінка показує журнал і блок «Сумарно переміщено»; підсумок у UI відповідає API.</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>REQ-RVW-UI</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>AC-03</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>Автодоповнення ресурсів обмежується вибраною категорією та відновлює повний список після її очищення.</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>REQ-RVW-UI</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>AC-04</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>Excel-експорт запускається з поточними фільтрами та формує справний файл .xlsx.</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>REQ-RVW-UI</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>AC-05</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>Перемикач групування доступний лише для category-only пошуку; за замовчуванням залишає найнижчі компоненти, а згорнуті рівні позначаються як «Згруповано».</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>REQ-RVW-UI</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>AC-06</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>Після явного вибору готового виробу та його напівфабрикату перемикач групування недоступний, а UI показує обидві декомпозиції без позначки згорнутого рівня.</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1075,113 +1101,79 @@
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">testId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">featureId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">acId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">title</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">description</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">priority</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">severity</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">status</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">testType</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">preconditions</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">expectedResult</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tags</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">author</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">jiraIssueKey</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">roleName</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">parameterized</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">dependencies</x:t>
-        </x:is>
+      <x:c r="A1" t="str">
+        <x:v>testId</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>featureId</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>acId</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>title</x:v>
+      </x:c>
+      <x:c r="E1" t="str">
+        <x:v>description</x:v>
+      </x:c>
+      <x:c r="F1" t="str">
+        <x:v>priority</x:v>
+      </x:c>
+      <x:c r="G1" t="str">
+        <x:v>severity</x:v>
+      </x:c>
+      <x:c r="H1" t="str">
+        <x:v>status</x:v>
+      </x:c>
+      <x:c r="I1" t="str">
+        <x:v>testType</x:v>
+      </x:c>
+      <x:c r="J1" t="str">
+        <x:v>preconditions</x:v>
+      </x:c>
+      <x:c r="K1" t="str">
+        <x:v>expectedResult</x:v>
+      </x:c>
+      <x:c r="L1" t="str">
+        <x:v>tags</x:v>
+      </x:c>
+      <x:c r="M1" t="str">
+        <x:v>author</x:v>
+      </x:c>
+      <x:c r="N1" t="str">
+        <x:v>jiraIssueKey</x:v>
+      </x:c>
+      <x:c r="O1" t="str">
+        <x:v>roleName</x:v>
+      </x:c>
+      <x:c r="P1" t="str">
+        <x:v>parameterized</x:v>
+      </x:c>
+      <x:c r="Q1" t="str">
+        <x:v>dependencies</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
-        <x:v>TC-RVW-BOM-001</x:v>
+        <x:v>TC-RVW-BOM-037</x:v>
       </x:c>
       <x:c r="B2" t="str">
         <x:v>REQ-RVW-BOM</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>AC-01</x:v>
+        <x:v>AC-16</x:v>
       </x:c>
       <x:c r="D2" t="str">
-        <x:v>BOM — пряма видача tracked Alcohol</x:v>
+        <x:v>BOM — reporting boundary не залежить від capabilities локації</x:v>
       </x:c>
       <x:c r="E2" t="str">
-        <x:v>Мета: Пряма видача Alcohol STORAGE→UNIT: journal isProduct=false; sum == sendAmount.</x:v>
+        <x:v>Мета: Unit-like LOCATION усередині TSUK розкладається; warehouse-like LOCATION поза TSUK — ні.</x:v>
       </x:c>
       <x:c r="F2" t="str">
         <x:v>HIGH</x:v>
       </x:c>
       <x:c r="G2" t="str">
-        <x:v>CRITICAL</x:v>
+        <x:v>BLOCKER</x:v>
       </x:c>
       <x:c r="H2" t="str">
         <x:v>ACTIVE</x:v>
@@ -1190,10 +1182,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J2" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging. @Admin підготував техкарти PRODUCTION + stock на OWNER_1 storage; receiver = UNIT storage.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging. @Admin підготував tech maps PRODUCTION і stock на дочірній локації TSUK_PARENT_UNITS; receiver — локація поза TSUK_PARENT_UNITS.</x:v>
       </x:c>
       <x:c r="K2" t="str">
-        <x:v>рядок isProduct=false; totallyUsage = sendAmount</x:v>
+        <x:v>Є лише TSUK relocation; Component = amount×2</x:v>
       </x:c>
       <x:c r="L2" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -1212,19 +1204,19 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
-        <x:v>TC-RVW-BOM-002</x:v>
+        <x:v>TC-RVW-BOM-001</x:v>
       </x:c>
       <x:c r="B3" t="str">
         <x:v>REQ-RVW-BOM</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>AC-02</x:v>
+        <x:v>AC-01</x:v>
       </x:c>
       <x:c r="D3" t="str">
-        <x:v>BOM — self-produced Product з Alcohol@2</x:v>
+        <x:v>BOM — пряма видача tracked Alcohol</x:v>
       </x:c>
       <x:c r="E3" t="str">
-        <x:v>Мета: Виробили Product → видача партії → sum = relocate × 2.</x:v>
+        <x:v>Мета: Пряма видача Alcohol з TSUK до зовнішньої структури: journal isProduct=false; sum == sendAmount.</x:v>
       </x:c>
       <x:c r="F3" t="str">
         <x:v>HIGH</x:v>
@@ -1239,10 +1231,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J3" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging. @Admin підготував техкарти PRODUCTION + stock на OWNER_1 storage; receiver = UNIT storage.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging. @Admin підготував tech maps PRODUCTION і stock на дочірній локації TSUK_PARENT_UNITS; receiver — локація поза TSUK_PARENT_UNITS.</x:v>
       </x:c>
       <x:c r="K3" t="str">
-        <x:v>Alcohol amount = relocate×2; isProduct=true</x:v>
+        <x:v>рядок isProduct=false; totallyUsage = sendAmount</x:v>
       </x:c>
       <x:c r="L3" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -1261,19 +1253,19 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
-        <x:v>TC-RVW-BOM-003</x:v>
+        <x:v>TC-RVW-BOM-002</x:v>
       </x:c>
       <x:c r="B4" t="str">
         <x:v>REQ-RVW-BOM</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>AC-03</x:v>
+        <x:v>AC-02</x:v>
       </x:c>
       <x:c r="D4" t="str">
-        <x:v>BOM — external FG, tech map fallback</x:v>
+        <x:v>BOM — self-produced Product з Alcohol@2</x:v>
       </x:c>
       <x:c r="E4" t="str">
-        <x:v>Мета: Партія без локального production → BOM з техкарти.</x:v>
+        <x:v>Мета: Виробили Product → видача партії → sum = relocate × 2.</x:v>
       </x:c>
       <x:c r="F4" t="str">
         <x:v>HIGH</x:v>
@@ -1288,10 +1280,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J4" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging. @Admin підготував техкарти PRODUCTION + stock на OWNER_1 storage; receiver = UNIT storage.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging. @Admin підготував tech maps PRODUCTION і stock на дочірній локації TSUK_PARENT_UNITS; receiver — локація поза TSUK_PARENT_UNITS.</x:v>
       </x:c>
       <x:c r="K4" t="str">
-        <x:v>Alcohol = relocate × usage з tech map</x:v>
+        <x:v>Alcohol amount = relocate×2; isProduct=true</x:v>
       </x:c>
       <x:c r="L4" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -1310,25 +1302,25 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
-        <x:v>TC-RVW-BOM-004</x:v>
+        <x:v>TC-RVW-BOM-003</x:v>
       </x:c>
       <x:c r="B5" t="str">
         <x:v>REQ-RVW-BOM</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>AC-04</x:v>
+        <x:v>AC-03</x:v>
       </x:c>
       <x:c r="D5" t="str">
-        <x:v>BOM — mixed produced + ready-made scale</x:v>
+        <x:v>BOM — external FG за історичною tech map</x:v>
       </x:c>
       <x:c r="E5" t="str">
-        <x:v>Мета: Produce 5 + supplier 5 → relocate 10; sum = 10×usage (scale path).</x:v>
+        <x:v>Мета: Підтверджена зовнішня партія розкладається за найновішою tech map, яка існувала на момент переміщення; для alternative group береться default.</x:v>
       </x:c>
       <x:c r="F5" t="str">
         <x:v>HIGH</x:v>
       </x:c>
       <x:c r="G5" t="str">
-        <x:v>MAJOR</x:v>
+        <x:v>CRITICAL</x:v>
       </x:c>
       <x:c r="H5" t="str">
         <x:v>ACTIVE</x:v>
@@ -1337,10 +1329,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J5" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging. @Admin підготував техкарти PRODUCTION + stock на OWNER_1 storage; receiver = UNIT storage.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging. @Admin підготував tech maps PRODUCTION і stock на дочірній локації TSUK_PARENT_UNITS; receiver — локація поза TSUK_PARENT_UNITS.</x:v>
       </x:c>
       <x:c r="K5" t="str">
-        <x:v>Alcohol = 10 × usage</x:v>
+        <x:v>Fixed і default alternative розраховані; non-default = 0</x:v>
       </x:c>
       <x:c r="L5" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -1359,25 +1351,25 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str">
-        <x:v>TC-RVW-BOM-010</x:v>
+        <x:v>TC-RVW-BOM-004</x:v>
       </x:c>
       <x:c r="B6" t="str">
         <x:v>REQ-RVW-BOM</x:v>
       </x:c>
       <x:c r="C6" t="str">
-        <x:v>AC-05</x:v>
+        <x:v>AC-04</x:v>
       </x:c>
       <x:c r="D6" t="str">
-        <x:v>BOM — depth 1</x:v>
+        <x:v>BOM — mixed produced + external незалежні алгоритми</x:v>
       </x:c>
       <x:c r="E6" t="str">
-        <x:v>Мета: Alcohol → Product (depth 1).</x:v>
+        <x:v>Мета: Produced-частина розкладається за фактичними inputs виробництва, external-частина — за історичною tech map з default alternative.</x:v>
       </x:c>
       <x:c r="F6" t="str">
         <x:v>HIGH</x:v>
       </x:c>
       <x:c r="G6" t="str">
-        <x:v>CRITICAL</x:v>
+        <x:v>MAJOR</x:v>
       </x:c>
       <x:c r="H6" t="str">
         <x:v>ACTIVE</x:v>
@@ -1386,10 +1378,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J6" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging. @Admin підготував техкарти PRODUCTION + stock на OWNER_1 storage; receiver = UNIT storage.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging. @Admin підготував tech maps PRODUCTION і stock на дочірній локації TSUK_PARENT_UNITS; receiver — локація поза TSUK_PARENT_UNITS.</x:v>
       </x:c>
       <x:c r="K6" t="str">
-        <x:v>sum = relocate × alcPerUnit</x:v>
+        <x:v>Produced використовує non-default; external використовує default; fixed враховано для всіх 10</x:v>
       </x:c>
       <x:c r="L6" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -1408,7 +1400,7 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
-        <x:v>TC-RVW-BOM-011</x:v>
+        <x:v>TC-RVW-BOM-010</x:v>
       </x:c>
       <x:c r="B7" t="str">
         <x:v>REQ-RVW-BOM</x:v>
@@ -1417,10 +1409,10 @@
         <x:v>AC-05</x:v>
       </x:c>
       <x:c r="D7" t="str">
-        <x:v>BOM — depth 2</x:v>
+        <x:v>BOM — depth 1</x:v>
       </x:c>
       <x:c r="E7" t="str">
-        <x:v>Мета: Alcohol → Semi → Product.</x:v>
+        <x:v>Мета: Alcohol → Product (depth 1).</x:v>
       </x:c>
       <x:c r="F7" t="str">
         <x:v>HIGH</x:v>
@@ -1435,10 +1427,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J7" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging. @Admin підготував техкарти PRODUCTION + stock на OWNER_1 storage; receiver = UNIT storage.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging. @Admin підготував tech maps PRODUCTION і stock на дочірній локації TSUK_PARENT_UNITS; receiver — локація поза TSUK_PARENT_UNITS.</x:v>
       </x:c>
       <x:c r="K7" t="str">
-        <x:v>sum = relocate×semi×alc</x:v>
+        <x:v>sum = relocate × alcPerUnit</x:v>
       </x:c>
       <x:c r="L7" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -1457,7 +1449,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str">
-        <x:v>TC-RVW-BOM-012</x:v>
+        <x:v>TC-RVW-BOM-011</x:v>
       </x:c>
       <x:c r="B8" t="str">
         <x:v>REQ-RVW-BOM</x:v>
@@ -1466,10 +1458,10 @@
         <x:v>AC-05</x:v>
       </x:c>
       <x:c r="D8" t="str">
-        <x:v>BOM — depth 3</x:v>
+        <x:v>BOM — depth 2</x:v>
       </x:c>
       <x:c r="E8" t="str">
-        <x:v>Мета: Alcohol → SF1 → SF2 → Product.</x:v>
+        <x:v>Мета: Alcohol → Semi → Product.</x:v>
       </x:c>
       <x:c r="F8" t="str">
         <x:v>HIGH</x:v>
@@ -1484,10 +1476,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J8" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging. @Admin підготував техкарти PRODUCTION + stock на OWNER_1 storage; receiver = UNIT storage.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging. @Admin підготував tech maps PRODUCTION і stock на дочірній локації TSUK_PARENT_UNITS; receiver — локація поза TSUK_PARENT_UNITS.</x:v>
       </x:c>
       <x:c r="K8" t="str">
-        <x:v>sum = добуток коефіцієнтів</x:v>
+        <x:v>sum = relocate×semi×alc</x:v>
       </x:c>
       <x:c r="L8" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -1506,19 +1498,19 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="str">
-        <x:v>TC-RVW-BOM-020</x:v>
+        <x:v>TC-RVW-BOM-012</x:v>
       </x:c>
       <x:c r="B9" t="str">
         <x:v>REQ-RVW-BOM</x:v>
       </x:c>
       <x:c r="C9" t="str">
-        <x:v>AC-06</x:v>
+        <x:v>AC-05</x:v>
       </x:c>
       <x:c r="D9" t="str">
-        <x:v>BOM — агрегація direct + nested</x:v>
+        <x:v>BOM — depth 3</x:v>
       </x:c>
       <x:c r="E9" t="str">
-        <x:v>Мета: Пряма видача Alcohol + Product зі Alcohol → одна sum.</x:v>
+        <x:v>Мета: Alcohol → SF1 → SF2 → Product.</x:v>
       </x:c>
       <x:c r="F9" t="str">
         <x:v>HIGH</x:v>
@@ -1533,10 +1525,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J9" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging. @Admin підготував техкарти PRODUCTION + stock на OWNER_1 storage; receiver = UNIT storage.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging. @Admin підготував tech maps PRODUCTION і stock на дочірній локації TSUK_PARENT_UNITS; receiver — локація поза TSUK_PARENT_UNITS.</x:v>
       </x:c>
       <x:c r="K9" t="str">
-        <x:v>sum = nested + direct</x:v>
+        <x:v>sum = добуток коефіцієнтів</x:v>
       </x:c>
       <x:c r="L9" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -1555,25 +1547,25 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="str">
-        <x:v>TC-RVW-BOM-021</x:v>
+        <x:v>TC-RVW-BOM-020</x:v>
       </x:c>
       <x:c r="B10" t="str">
         <x:v>REQ-RVW-BOM</x:v>
       </x:c>
       <x:c r="C10" t="str">
-        <x:v>AC-07</x:v>
+        <x:v>AC-06</x:v>
       </x:c>
       <x:c r="D10" t="str">
-        <x:v>BOM — mid-level як product і ingredient</x:v>
+        <x:v>BOM — агрегація direct + nested</x:v>
       </x:c>
       <x:c r="E10" t="str">
-        <x:v>Мета: resourceIds=[Semi]: видача Semi + видача Product зі Semi.</x:v>
+        <x:v>Мета: Пряма видача Alcohol + Product зі Alcohol → одна sum.</x:v>
       </x:c>
       <x:c r="F10" t="str">
         <x:v>HIGH</x:v>
       </x:c>
       <x:c r="G10" t="str">
-        <x:v>MAJOR</x:v>
+        <x:v>CRITICAL</x:v>
       </x:c>
       <x:c r="H10" t="str">
         <x:v>ACTIVE</x:v>
@@ -1582,10 +1574,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J10" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging. @Admin підготував техкарти PRODUCTION + stock на OWNER_1 storage; receiver = UNIT storage.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging. @Admin підготував tech maps PRODUCTION і stock на дочірній локації TSUK_PARENT_UNITS; receiver — локація поза TSUK_PARENT_UNITS.</x:v>
       </x:c>
       <x:c r="K10" t="str">
-        <x:v>обидва рядки; sum = direct + nested</x:v>
+        <x:v>sum = nested + direct</x:v>
       </x:c>
       <x:c r="L10" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -1604,19 +1596,19 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="str">
-        <x:v>TC-RVW-BOM-022</x:v>
+        <x:v>TC-RVW-BOM-021</x:v>
       </x:c>
       <x:c r="B11" t="str">
         <x:v>REQ-RVW-BOM</x:v>
       </x:c>
       <x:c r="C11" t="str">
-        <x:v>AC-08</x:v>
+        <x:v>AC-07</x:v>
       </x:c>
       <x:c r="D11" t="str">
-        <x:v>BOM — unrelated product excluded</x:v>
+        <x:v>BOM — mid-level як product і ingredient</x:v>
       </x:c>
       <x:c r="E11" t="str">
-        <x:v>Мета: Product без Alcohol не в journal при resourceIds=[Alcohol].</x:v>
+        <x:v>Мета: resourceIds=[Semi]: видача Semi + видача Product зі Semi.</x:v>
       </x:c>
       <x:c r="F11" t="str">
         <x:v>HIGH</x:v>
@@ -1631,10 +1623,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J11" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging. @Admin підготував техкарти PRODUCTION + stock на OWNER_1 storage; receiver = UNIT storage.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging. @Admin підготував tech maps PRODUCTION і stock на дочірній локації TSUK_PARENT_UNITS; receiver — локація поза TSUK_PARENT_UNITS.</x:v>
       </x:c>
       <x:c r="K11" t="str">
-        <x:v>sum=0; relocation відсутній</x:v>
+        <x:v>обидва рядки; sum = direct + nested</x:v>
       </x:c>
       <x:c r="L11" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -1653,25 +1645,25 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="str">
-        <x:v>TC-RVW-ALT-001</x:v>
+        <x:v>TC-RVW-BOM-022</x:v>
       </x:c>
       <x:c r="B12" t="str">
         <x:v>REQ-RVW-BOM</x:v>
       </x:c>
       <x:c r="C12" t="str">
-        <x:v>AC-09</x:v>
+        <x:v>AC-08</x:v>
       </x:c>
       <x:c r="D12" t="str">
-        <x:v>BOM alt — non-default alternative counted</x:v>
+        <x:v>BOM — unrelated product excluded</x:v>
       </x:c>
       <x:c r="E12" t="str">
-        <x:v>Мета: Фактичний non-default input з production_process_input потрапляє в sum.</x:v>
+        <x:v>Мета: Product без Alcohol не в journal при resourceIds=[Alcohol].</x:v>
       </x:c>
       <x:c r="F12" t="str">
         <x:v>HIGH</x:v>
       </x:c>
       <x:c r="G12" t="str">
-        <x:v>CRITICAL</x:v>
+        <x:v>MAJOR</x:v>
       </x:c>
       <x:c r="H12" t="str">
         <x:v>ACTIVE</x:v>
@@ -1680,13 +1672,13 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J12" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging. @Admin підготував техкарти PRODUCTION + stock на OWNER_1 storage; receiver = UNIT storage.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging. @Admin підготував tech maps PRODUCTION і stock на дочірній локації TSUK_PARENT_UNITS; receiver — локація поза TSUK_PARENT_UNITS.</x:v>
       </x:c>
       <x:c r="K12" t="str">
-        <x:v>amount = usage×relocate</x:v>
+        <x:v>sum=0; relocation відсутній</x:v>
       </x:c>
       <x:c r="L12" t="str">
-        <x:v>resource-viewer,api,alt-groups</x:v>
+        <x:v>resource-viewer,api</x:v>
       </x:c>
       <x:c r="M12" t="str">
         <x:v>QA</x:v>
@@ -1702,7 +1694,7 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
-        <x:v>TC-RVW-ALT-002</x:v>
+        <x:v>TC-RVW-ALT-001</x:v>
       </x:c>
       <x:c r="B13" t="str">
         <x:v>REQ-RVW-BOM</x:v>
@@ -1711,10 +1703,10 @@
         <x:v>AC-09</x:v>
       </x:c>
       <x:c r="D13" t="str">
-        <x:v>BOM alt — default alternative counted</x:v>
+        <x:v>BOM alt — non-default alternative counted</x:v>
       </x:c>
       <x:c r="E13" t="str">
-        <x:v>Мета: Default alternative з production_process_input враховується.</x:v>
+        <x:v>Мета: Фактичний non-default input з production_process_input потрапляє в sum.</x:v>
       </x:c>
       <x:c r="F13" t="str">
         <x:v>HIGH</x:v>
@@ -1729,10 +1721,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J13" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging. @Admin підготував техкарти PRODUCTION + stock на OWNER_1 storage; receiver = UNIT storage.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging. @Admin підготував tech maps PRODUCTION і stock на дочірній локації TSUK_PARENT_UNITS; receiver — локація поза TSUK_PARENT_UNITS.</x:v>
       </x:c>
       <x:c r="K13" t="str">
-        <x:v>amount коректний</x:v>
+        <x:v>amount = usage×relocate</x:v>
       </x:c>
       <x:c r="L13" t="str">
         <x:v>resource-viewer,api,alt-groups</x:v>
@@ -1751,19 +1743,19 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
-        <x:v>TC-RVW-BOM-030</x:v>
+        <x:v>TC-RVW-ALT-002</x:v>
       </x:c>
       <x:c r="B14" t="str">
         <x:v>REQ-RVW-BOM</x:v>
       </x:c>
       <x:c r="C14" t="str">
-        <x:v>AC-10</x:v>
+        <x:v>AC-09</x:v>
       </x:c>
       <x:c r="D14" t="str">
-        <x:v>BOM — blending двох production в один batch</x:v>
+        <x:v>BOM alt — default alternative counted</x:v>
       </x:c>
       <x:c r="E14" t="str">
-        <x:v>Мета: Один batch number, різні рецепти → зважене середнє, не сума.</x:v>
+        <x:v>Мета: Default alternative з production_process_input враховується.</x:v>
       </x:c>
       <x:c r="F14" t="str">
         <x:v>HIGH</x:v>
@@ -1778,13 +1770,13 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J14" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging. @Admin підготував техкарти PRODUCTION + stock на OWNER_1 storage; receiver = UNIT storage.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging. @Admin підготував tech maps PRODUCTION і stock на дочірній локації TSUK_PARENT_UNITS; receiver — локація поза TSUK_PARENT_UNITS.</x:v>
       </x:c>
       <x:c r="K14" t="str">
-        <x:v>Alcohol = 32 (per-unit 3.2)</x:v>
+        <x:v>amount коректний</x:v>
       </x:c>
       <x:c r="L14" t="str">
-        <x:v>resource-viewer,api</x:v>
+        <x:v>resource-viewer,api,alt-groups</x:v>
       </x:c>
       <x:c r="M14" t="str">
         <x:v>QA</x:v>
@@ -1800,19 +1792,19 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
-        <x:v>TC-RVW-BOM-031</x:v>
+        <x:v>TC-RVW-BOM-030</x:v>
       </x:c>
       <x:c r="B15" t="str">
         <x:v>REQ-RVW-BOM</x:v>
       </x:c>
       <x:c r="C15" t="str">
-        <x:v>AC-11</x:v>
+        <x:v>AC-10</x:v>
       </x:c>
       <x:c r="D15" t="str">
-        <x:v>BOM — item без партій → tech map</x:v>
+        <x:v>BOM — останнє production для shared batch</x:v>
       </x:c>
       <x:c r="E15" t="str">
-        <x:v>Мета: Send Product без batches → повний обсяг через tech map.</x:v>
+        <x:v>Мета: Один batch number і кілька production records з різними фактичними витратами → використовується останній запис.</x:v>
       </x:c>
       <x:c r="F15" t="str">
         <x:v>HIGH</x:v>
@@ -1827,10 +1819,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J15" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging. @Admin підготував техкарти PRODUCTION + stock на OWNER_1 storage; receiver = UNIT storage.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging. @Admin підготував tech maps PRODUCTION і stock на дочірній локації TSUK_PARENT_UNITS; receiver — локація поза TSUK_PARENT_UNITS.</x:v>
       </x:c>
       <x:c r="K15" t="str">
-        <x:v>Alcohol = relocate × usage</x:v>
+        <x:v>Alcohol = 40 за останнім usage4</x:v>
       </x:c>
       <x:c r="L15" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -1849,19 +1841,19 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
-        <x:v>TC-RVW-BOM-032</x:v>
+        <x:v>TC-RVW-BOM-031</x:v>
       </x:c>
       <x:c r="B16" t="str">
         <x:v>REQ-RVW-BOM</x:v>
       </x:c>
       <x:c r="C16" t="str">
-        <x:v>AC-12</x:v>
+        <x:v>AC-11</x:v>
       </x:c>
       <x:c r="D16" t="str">
-        <x:v>BOM — версія техкарти на дату видачі (історична)</x:v>
+        <x:v>BOM — item без партій → tech map</x:v>
       </x:c>
       <x:c r="E16" t="str">
-        <x:v>Мета: LocalDate=startOfDay UTC: дата до createdAt → MIN(id)=V1; дата після обох → newest V2.</x:v>
+        <x:v>Мета: Send Product без batches → повний обсяг через tech map.</x:v>
       </x:c>
       <x:c r="F16" t="str">
         <x:v>HIGH</x:v>
@@ -1876,10 +1868,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J16" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging. @Admin підготував техкарти PRODUCTION + stock на OWNER_1 storage; receiver = UNIT storage.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging. @Admin підготував tech maps PRODUCTION і stock на дочірній локації TSUK_PARENT_UNITS; receiver — локація поза TSUK_PARENT_UNITS.</x:v>
       </x:c>
       <x:c r="K16" t="str">
-        <x:v>past×2; future×5</x:v>
+        <x:v>Alcohol = relocate × usage</x:v>
       </x:c>
       <x:c r="L16" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -1898,25 +1890,25 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
-        <x:v>TC-RVW-BOM-033</x:v>
+        <x:v>TC-RVW-BOM-032</x:v>
       </x:c>
       <x:c r="B17" t="str">
         <x:v>REQ-RVW-BOM</x:v>
       </x:c>
       <x:c r="C17" t="str">
-        <x:v>AC-13</x:v>
+        <x:v>AC-12</x:v>
       </x:c>
       <x:c r="D17" t="str">
-        <x:v>BOM — цикл рецептів не infinite</x:v>
+        <x:v>BOM — версія техкарти на дату видачі (історична)</x:v>
       </x:c>
       <x:c r="E17" t="str">
-        <x:v>Мета: A←B←A: expand зупиняється на path; B один раз.</x:v>
+        <x:v>Мета: Для інвентаризаційного залишку використовується найновіша карта, що вже існувала на момент переміщення; майбутня карта історію не змінює.</x:v>
       </x:c>
       <x:c r="F17" t="str">
         <x:v>HIGH</x:v>
       </x:c>
       <x:c r="G17" t="str">
-        <x:v>MAJOR</x:v>
+        <x:v>CRITICAL</x:v>
       </x:c>
       <x:c r="H17" t="str">
         <x:v>ACTIVE</x:v>
@@ -1925,10 +1917,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J17" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging. @Admin підготував техкарти PRODUCTION + stock на OWNER_1 storage; receiver = UNIT storage.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging. @Admin підготував tech maps PRODUCTION і stock на дочірній локації TSUK_PARENT_UNITS; receiver — локація поза TSUK_PARENT_UNITS.</x:v>
       </x:c>
       <x:c r="K17" t="str">
-        <x:v>totallyUsage = amount; без дубля</x:v>
+        <x:v>Обидва історичні склади не змінилися</x:v>
       </x:c>
       <x:c r="L17" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -1947,19 +1939,19 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
-        <x:v>TC-RVW-BOM-034</x:v>
+        <x:v>TC-RVW-BOM-033</x:v>
       </x:c>
       <x:c r="B18" t="str">
         <x:v>REQ-RVW-BOM</x:v>
       </x:c>
       <x:c r="C18" t="str">
-        <x:v>AC-14</x:v>
+        <x:v>AC-13</x:v>
       </x:c>
       <x:c r="D18" t="str">
-        <x:v>BOM — scale-down (legacy producedQty &gt; amount)</x:v>
+        <x:v>BOM — цикл рецептів не infinite</x:v>
       </x:c>
       <x:c r="E18" t="str">
-        <x:v>Мета: Партії claim більше за amount рядка: sum = amount×usage (не producedQty×usage). Arrange: produce+relocate; DB shrink relocation_item.amount.</x:v>
+        <x:v>Мета: A←B←C←A: expand повертає A-B-C, зупиняється перед повторним A і не дублює компоненти.</x:v>
       </x:c>
       <x:c r="F18" t="str">
         <x:v>HIGH</x:v>
@@ -1974,10 +1966,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J18" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging. @Admin підготував техкарти PRODUCTION + stock на OWNER_1 storage; receiver = UNIT storage. Доступ до БД (use.database).</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging. @Admin підготував tech maps PRODUCTION і stock на дочірній локації TSUK_PARENT_UNITS; receiver — локація поза TSUK_PARENT_UNITS.</x:v>
       </x:c>
       <x:c r="K18" t="str">
-        <x:v>amount×usage; не повний producedQty×usage</x:v>
+        <x:v>Ingredients містять A, B і C по одному разу; повторного A немає</x:v>
       </x:c>
       <x:c r="L18" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -1996,25 +1988,25 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="str">
-        <x:v>TC-RVW-001</x:v>
+        <x:v>TC-RVW-BOM-034</x:v>
       </x:c>
       <x:c r="B19" t="str">
-        <x:v>REQ-RVW-FILTER</x:v>
+        <x:v>REQ-RVW-BOM</x:v>
       </x:c>
       <x:c r="C19" t="str">
-        <x:v>AC-08</x:v>
+        <x:v>AC-14</x:v>
       </x:c>
       <x:c r="D19" t="str">
-        <x:v>API — sums сортування + pre-seed amount=0 (regression)</x:v>
+        <x:v>BOM — scale-down (legacy producedQty &gt; amount)</x:v>
       </x:c>
       <x:c r="E19" t="str">
-        <x:v>Мета: GET /relocations → sums: порядок і amount=0 без руху. Відомий дефект tk: empty BOM → sums=[]; очікується pre-seed нулів.</x:v>
+        <x:v>Мета: Партії claim більше за amount рядка: sum = amount×usage (не producedQty×usage). Arrange: produce+relocate; DB shrink relocation_item.amount.</x:v>
       </x:c>
       <x:c r="F19" t="str">
         <x:v>HIGH</x:v>
       </x:c>
       <x:c r="G19" t="str">
-        <x:v>CRITICAL</x:v>
+        <x:v>MAJOR</x:v>
       </x:c>
       <x:c r="H19" t="str">
         <x:v>ACTIVE</x:v>
@@ -2023,10 +2015,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J19" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging. @Admin підготував tech maps PRODUCTION і stock на дочірній локації TSUK_PARENT_UNITS; receiver — локація поза TSUK_PARENT_UNITS. Доступ до БД (use.database).</x:v>
       </x:c>
       <x:c r="K19" t="str">
-        <x:v>До фіксу: sums=[]; після фіксу: 111→…→їжа, нулі</x:v>
+        <x:v>amount×usage; не повний producedQty×usage</x:v>
       </x:c>
       <x:c r="L19" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -2045,19 +2037,19 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="str">
-        <x:v>TC-RVW-API-001</x:v>
+        <x:v>TC-RVW-BOM-035</x:v>
       </x:c>
       <x:c r="B20" t="str">
-        <x:v>REQ-RVW</x:v>
+        <x:v>REQ-RVW-BOM</x:v>
       </x:c>
       <x:c r="C20" t="str">
-        <x:v>AC-01</x:v>
+        <x:v>AC-15</x:v>
       </x:c>
       <x:c r="D20" t="str">
-        <x:v>API — my-units без UNIT для ResourceViewer</x:v>
+        <x:v>BOM — до першої tech map ресурс атомарний</x:v>
       </x:c>
       <x:c r="E20" t="str">
-        <x:v>Мета: Селектор my-units: лише STORAGE/PRODUCTION.</x:v>
+        <x:v>Мета: Якщо на момент переміщення не існувало жодної tech map, пізніше створена карта не змінює історичний склад.</x:v>
       </x:c>
       <x:c r="F20" t="str">
         <x:v>HIGH</x:v>
@@ -2072,13 +2064,13 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J20" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging. @Admin підготував tech maps PRODUCTION і stock на дочірній локації TSUK_PARENT_UNITS; receiver — локація поза TSUK_PARENT_UNITS.</x:v>
       </x:c>
       <x:c r="K20" t="str">
-        <x:v>OK</x:v>
+        <x:v>Component відсутній; Product лишається атомарним, isProduct=false</x:v>
       </x:c>
       <x:c r="L20" t="str">
-        <x:v>resource-viewer,api,my-units</x:v>
+        <x:v>resource-viewer,api</x:v>
       </x:c>
       <x:c r="M20" t="str">
         <x:v>QA</x:v>
@@ -2094,19 +2086,19 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="str">
-        <x:v>TC-RVW-API-002</x:v>
+        <x:v>TC-RVW-BOM-036</x:v>
       </x:c>
       <x:c r="B21" t="str">
-        <x:v>REQ-RVW-FILTER</x:v>
+        <x:v>REQ-RVW-BOM</x:v>
       </x:c>
       <x:c r="C21" t="str">
-        <x:v>AC-07</x:v>
+        <x:v>AC-15</x:v>
       </x:c>
       <x:c r="D21" t="str">
-        <x:v>API — journal лише STORAGE/PRODUCTION→UNIT</x:v>
+        <x:v>BOM — зовнішня партія до першої tech map атомарна</x:v>
       </x:c>
       <x:c r="E21" t="str">
-        <x:v>Мета: У журналі видно STORAGE/PRODUCTION→UNIT; UNIT→UNIT приховано.</x:v>
+        <x:v>Мета: Зовнішньо отримана партія, переміщена до появи першої tech map, лишається атомарною; пізніше створена карта не змінює історичний склад.</x:v>
       </x:c>
       <x:c r="F21" t="str">
         <x:v>HIGH</x:v>
@@ -2121,10 +2113,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J21" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging. @Admin підготував tech maps PRODUCTION і stock на дочірній локації TSUK_PARENT_UNITS; receiver — локація поза TSUK_PARENT_UNITS.</x:v>
       </x:c>
       <x:c r="K21" t="str">
-        <x:v>Є STORAGE/PRODUCTION→UNIT; немає UNIT→UNIT</x:v>
+        <x:v>Один атомарний рядок Product, isProduct=false</x:v>
       </x:c>
       <x:c r="L21" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -2143,25 +2135,25 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
-        <x:v>TC-RVW-API-003</x:v>
+        <x:v>TC-RVW-001</x:v>
       </x:c>
       <x:c r="B22" t="str">
         <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>AC-07</x:v>
+        <x:v>AC-08</x:v>
       </x:c>
       <x:c r="D22" t="str">
-        <x:v>API — UNIT→CREW excluded from sums</x:v>
+        <x:v>API — sums сортування + pre-seed amount=0 (regression)</x:v>
       </x:c>
       <x:c r="E22" t="str">
-        <x:v>Мета: UNIT→CREW не в sums з GET /relocations.</x:v>
+        <x:v>Мета: GET /relocations → sums: порядок і amount=0 без руху. Відомий дефект tk: empty BOM → sums=[]; очікується pre-seed нулів.</x:v>
       </x:c>
       <x:c r="F22" t="str">
         <x:v>HIGH</x:v>
       </x:c>
       <x:c r="G22" t="str">
-        <x:v>MAJOR</x:v>
+        <x:v>CRITICAL</x:v>
       </x:c>
       <x:c r="H22" t="str">
         <x:v>ACTIVE</x:v>
@@ -2170,10 +2162,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J22" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging.</x:v>
       </x:c>
       <x:c r="K22" t="str">
-        <x:v>amount=0</x:v>
+        <x:v>До фіксу: sums=[]; після фіксу: 111→…→їжа, нулі</x:v>
       </x:c>
       <x:c r="L22" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -2192,19 +2184,19 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
-        <x:v>TC-RVW-API-010</x:v>
+        <x:v>TC-RVW-API-001</x:v>
       </x:c>
       <x:c r="B23" t="str">
-        <x:v>REQ-RVW-FILTER</x:v>
+        <x:v>REQ-RVW</x:v>
       </x:c>
       <x:c r="C23" t="str">
         <x:v>AC-01</x:v>
       </x:c>
       <x:c r="D23" t="str">
-        <x:v>API — categoryIds як tracking target</x:v>
+        <x:v>API — глобальному ResourceViewer не потрібен my-units</x:v>
       </x:c>
       <x:c r="E23" t="str">
-        <x:v>Мета: Без resourceIds: інгредієнти категорії A трекаються; pre-seed нулів вимкнений.</x:v>
+        <x:v>Мета: Глобальна роль не має location grants; /my-units недоступний, viewer endpoints доступні.</x:v>
       </x:c>
       <x:c r="F23" t="str">
         <x:v>HIGH</x:v>
@@ -2219,13 +2211,13 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J23" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging.</x:v>
       </x:c>
       <x:c r="K23" t="str">
-        <x:v>A у sum; B відсутній</x:v>
+        <x:v>HTTP 200 без my-units</x:v>
       </x:c>
       <x:c r="L23" t="str">
-        <x:v>resource-viewer,api</x:v>
+        <x:v>resource-viewer,api,my-units</x:v>
       </x:c>
       <x:c r="M23" t="str">
         <x:v>QA</x:v>
@@ -2241,19 +2233,19 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str">
-        <x:v>TC-RVW-API-011</x:v>
+        <x:v>TC-RVW-API-002</x:v>
       </x:c>
       <x:c r="B24" t="str">
         <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="C24" t="str">
-        <x:v>AC-02</x:v>
+        <x:v>AC-07</x:v>
       </x:c>
       <x:c r="D24" t="str">
-        <x:v>API — supplier AND-фільтр</x:v>
+        <x:v>API — journal відбирає перетин reporting boundary</x:v>
       </x:c>
       <x:c r="E24" t="str">
-        <x:v>Мета: Постачальник збігається → sum&gt;0; інший → 0.</x:v>
+        <x:v>Мета: У журналі видно переміщення з TSUK назовні; подальше переміщення між зовнішніми локаціями приховано.</x:v>
       </x:c>
       <x:c r="F24" t="str">
         <x:v>HIGH</x:v>
@@ -2268,10 +2260,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J24" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging.</x:v>
       </x:c>
       <x:c r="K24" t="str">
-        <x:v>Match&gt;0; Other=0</x:v>
+        <x:v>Є два TSUK→outside; outside→outside відсутнє</x:v>
       </x:c>
       <x:c r="L24" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -2290,25 +2282,25 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="str">
-        <x:v>TC-RVW-API-012</x:v>
+        <x:v>TC-RVW-API-003</x:v>
       </x:c>
       <x:c r="B25" t="str">
         <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="C25" t="str">
-        <x:v>AC-03</x:v>
+        <x:v>AC-07</x:v>
       </x:c>
       <x:c r="D25" t="str">
-        <x:v>API — start/end date range</x:v>
+        <x:v>API — downstream relocation поза TSUK excluded from sums</x:v>
       </x:c>
       <x:c r="E25" t="str">
-        <x:v>Мета: Період відсікає переміщення поза діапазоном.</x:v>
+        <x:v>Мета: Подальша передача до CREW/FLY_POINT поза reporting boundary не входить до sums.</x:v>
       </x:c>
       <x:c r="F25" t="str">
         <x:v>HIGH</x:v>
       </x:c>
       <x:c r="G25" t="str">
-        <x:v>CRITICAL</x:v>
+        <x:v>MAJOR</x:v>
       </x:c>
       <x:c r="H25" t="str">
         <x:v>ACTIVE</x:v>
@@ -2317,10 +2309,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J25" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging.</x:v>
       </x:c>
       <x:c r="K25" t="str">
-        <x:v>in: сума&gt;0; out: 0</x:v>
+        <x:v>amount=0</x:v>
       </x:c>
       <x:c r="L25" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -2339,25 +2331,25 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str">
-        <x:v>TC-RVW-API-013</x:v>
+        <x:v>TC-RVW-API-022</x:v>
       </x:c>
       <x:c r="B26" t="str">
         <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>AC-04</x:v>
+        <x:v>AC-07</x:v>
       </x:c>
       <x:c r="D26" t="str">
-        <x:v>API — empty guards</x:v>
+        <x:v>API — ієрархія має пріоритет над capabilities локації</x:v>
       </x:c>
       <x:c r="E26" t="str">
-        <x:v>Мета: Без tracking target або без receiver filter → content=[].</x:v>
+        <x:v>Мета: Unit-like LOCATION у TSUK і її вкладений нащадок входять до journal; warehouse-like LOCATION поза TSUK та внутрішній TSUK route виключаються.</x:v>
       </x:c>
       <x:c r="F26" t="str">
         <x:v>HIGH</x:v>
       </x:c>
       <x:c r="G26" t="str">
-        <x:v>CRITICAL</x:v>
+        <x:v>BLOCKER</x:v>
       </x:c>
       <x:c r="H26" t="str">
         <x:v>ACTIVE</x:v>
@@ -2366,10 +2358,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J26" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging.</x:v>
       </x:c>
       <x:c r="K26" t="str">
-        <x:v>content=[]</x:v>
+        <x:v>Journal містить лише direct і nested TSUK→outside relocation; sums дорівнює сумі цих двох переміщень незалежно від features.</x:v>
       </x:c>
       <x:c r="L26" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -2388,25 +2380,25 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="str">
-        <x:v>TC-RVW-API-014</x:v>
+        <x:v>TC-RVW-API-023</x:v>
       </x:c>
       <x:c r="B27" t="str">
         <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>AC-05</x:v>
+        <x:v>AC-06</x:v>
       </x:c>
       <x:c r="D27" t="str">
-        <x:v>API — пагінація journal + date DESC</x:v>
+        <x:v>API — Excel export використовує reporting boundary</x:v>
       </x:c>
       <x:c r="E27" t="str">
-        <x:v>Мета: page metadata; рядки відсортовані за датою desc.</x:v>
+        <x:v>Мета: Export містить unit-like source з TSUK і не містить warehouse-like source поза TSUK.</x:v>
       </x:c>
       <x:c r="F27" t="str">
         <x:v>HIGH</x:v>
       </x:c>
       <x:c r="G27" t="str">
-        <x:v>MAJOR</x:v>
+        <x:v>CRITICAL</x:v>
       </x:c>
       <x:c r="H27" t="str">
         <x:v>ACTIVE</x:v>
@@ -2415,10 +2407,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J27" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging.</x:v>
       </x:c>
       <x:c r="K27" t="str">
-        <x:v>dates DESC</x:v>
+        <x:v>Є TSUK source; outside source відсутнє</x:v>
       </x:c>
       <x:c r="L27" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -2437,19 +2429,19 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="str">
-        <x:v>TC-RVW-API-015</x:v>
+        <x:v>TC-RVW-API-010</x:v>
       </x:c>
       <x:c r="B28" t="str">
         <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>AC-09</x:v>
+        <x:v>AC-01</x:v>
       </x:c>
       <x:c r="D28" t="str">
-        <x:v>API — UI states виключають CANCELLED/RETURNED</x:v>
+        <x:v>API — categoryIds як tracking target</x:v>
       </x:c>
       <x:c r="E28" t="str">
-        <x:v>Мета: Активна видача: UI states видно; states=CANCELLED|RETURNED — ні. Якщо RETURNED (API/DB): з UI states зникає.</x:v>
+        <x:v>Мета: Без resourceIds: інгредієнти категорії A трекаються; pre-seed нулів вимкнений.</x:v>
       </x:c>
       <x:c r="F28" t="str">
         <x:v>HIGH</x:v>
@@ -2464,10 +2456,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J28" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging.</x:v>
       </x:c>
       <x:c r="K28" t="str">
-        <x:v>немає рядка; sum≈0</x:v>
+        <x:v>A у sum; B відсутній</x:v>
       </x:c>
       <x:c r="L28" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -2486,19 +2478,19 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="str">
-        <x:v>TC-RVW-API-016</x:v>
+        <x:v>TC-RVW-API-011</x:v>
       </x:c>
       <x:c r="B29" t="str">
         <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>AC-10</x:v>
+        <x:v>AC-02</x:v>
       </x:c>
       <x:c r="D29" t="str">
-        <x:v>API — отримувачі ПМ 414 / СБС / Інші</x:v>
+        <x:v>API — supplier AND-фільтр</x:v>
       </x:c>
       <x:c r="E29" t="str">
-        <x:v>Мета: unitsOther=Інші включає типовий UNIT; unit414Pm і СБС без ПМ — ні.</x:v>
+        <x:v>Мета: Постачальник збігається → sum&gt;0; інший → 0.</x:v>
       </x:c>
       <x:c r="F29" t="str">
         <x:v>HIGH</x:v>
@@ -2513,10 +2505,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J29" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging.</x:v>
       </x:c>
       <x:c r="K29" t="str">
-        <x:v>немає relocation</x:v>
+        <x:v>Match&gt;0; Other=0</x:v>
       </x:c>
       <x:c r="L29" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -2535,25 +2527,25 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
-        <x:v>TC-RVW-API-017</x:v>
+        <x:v>TC-RVW-API-012</x:v>
       </x:c>
       <x:c r="B30" t="str">
         <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>AC-10</x:v>
+        <x:v>AC-03</x:v>
       </x:c>
       <x:c r="D30" t="str">
-        <x:v>API — receiverIds AND unit414Pm</x:v>
+        <x:v>API — start/end date range</x:v>
       </x:c>
       <x:c r="E30" t="str">
-        <x:v>Мета: Перетин явного receiverIds з ПМ 414 порожній, якщо UNIT поза ПМ.</x:v>
+        <x:v>Мета: Період відсікає переміщення поза діапазоном.</x:v>
       </x:c>
       <x:c r="F30" t="str">
         <x:v>HIGH</x:v>
       </x:c>
       <x:c r="G30" t="str">
-        <x:v>MAJOR</x:v>
+        <x:v>CRITICAL</x:v>
       </x:c>
       <x:c r="H30" t="str">
         <x:v>ACTIVE</x:v>
@@ -2562,10 +2554,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J30" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging.</x:v>
       </x:c>
       <x:c r="K30" t="str">
-        <x:v>content=[]; sum=0</x:v>
+        <x:v>in: сума&gt;0; out: 0</x:v>
       </x:c>
       <x:c r="L30" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -2584,19 +2576,19 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str">
-        <x:v>TC-RVW-API-018</x:v>
+        <x:v>TC-RVW-API-013</x:v>
       </x:c>
       <x:c r="B31" t="str">
         <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="C31" t="str">
-        <x:v>AC-11</x:v>
+        <x:v>AC-04</x:v>
       </x:c>
       <x:c r="D31" t="str">
-        <x:v>API — категорія не дублює переміщення продукту та його компонента</x:v>
+        <x:v>API — empty guards</x:v>
       </x:c>
       <x:c r="E31" t="str">
-        <x:v>Мета: Гарантувати один рядок журналу для однієї фізичної передачі, коли продукт і його компонент належать до вибраної категорії.</x:v>
+        <x:v>Мета: Без tracking target або без receiver filter → content=[].</x:v>
       </x:c>
       <x:c r="F31" t="str">
         <x:v>HIGH</x:v>
@@ -2611,10 +2603,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J31" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging.</x:v>
       </x:c>
       <x:c r="K31" t="str">
-        <x:v>Передача продукту A присутня в content рівно один раз за relocationId; єдиний рядок містить продукт A та компонент Б у ingredients.</x:v>
+        <x:v>content=[]</x:v>
       </x:c>
       <x:c r="L31" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -2633,25 +2625,25 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="str">
-        <x:v>TC-RVW-API-020</x:v>
+        <x:v>TC-RVW-API-014</x:v>
       </x:c>
       <x:c r="B32" t="str">
         <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="C32" t="str">
-        <x:v>AC-06</x:v>
+        <x:v>AC-05</x:v>
       </x:c>
       <x:c r="D32" t="str">
-        <x:v>API — Excel export</x:v>
+        <x:v>API — пагінація journal + date DESC</x:v>
       </x:c>
       <x:c r="E32" t="str">
-        <x:v>Мета: Валідний фільтр → .xlsx непорожній; guard → порожнє тіло.</x:v>
+        <x:v>Мета: page metadata; рядки відсортовані за датою desc.</x:v>
       </x:c>
       <x:c r="F32" t="str">
         <x:v>HIGH</x:v>
       </x:c>
       <x:c r="G32" t="str">
-        <x:v>CRITICAL</x:v>
+        <x:v>MAJOR</x:v>
       </x:c>
       <x:c r="H32" t="str">
         <x:v>ACTIVE</x:v>
@@ -2660,10 +2652,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J32" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging.</x:v>
       </x:c>
       <x:c r="K32" t="str">
-        <x:v>200; body порожній</x:v>
+        <x:v>dates DESC</x:v>
       </x:c>
       <x:c r="L32" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -2682,25 +2674,25 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="str">
-        <x:v>TC-UI-RES-AC-001</x:v>
+        <x:v>TC-RVW-API-015</x:v>
       </x:c>
       <x:c r="B33" t="str">
-        <x:v>REQ-RVW-UI</x:v>
+        <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="C33" t="str">
-        <x:v>AC-03</x:v>
+        <x:v>AC-09</x:v>
       </x:c>
       <x:c r="D33" t="str">
-        <x:v>UI — autocomplete з фільтром категорії</x:v>
+        <x:v>API — UI states виключають CANCELLED/RETURNED</x:v>
       </x:c>
       <x:c r="E33" t="str">
-        <x:v>Мета: Категорія A: autocomplete показує ресурс A, не B.</x:v>
+        <x:v>Мета: Активна видача: UI states видно; states=CANCELLED|RETURNED — ні. Якщо RETURNED (API/DB): з UI states зникає.</x:v>
       </x:c>
       <x:c r="F33" t="str">
         <x:v>HIGH</x:v>
       </x:c>
       <x:c r="G33" t="str">
-        <x:v>MAJOR</x:v>
+        <x:v>CRITICAL</x:v>
       </x:c>
       <x:c r="H33" t="str">
         <x:v>ACTIVE</x:v>
@@ -2709,13 +2701,13 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J33" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging.</x:v>
       </x:c>
       <x:c r="K33" t="str">
-        <x:v>є A і B</x:v>
+        <x:v>немає рядка; sum≈0</x:v>
       </x:c>
       <x:c r="L33" t="str">
-        <x:v>resource-viewer,ui</x:v>
+        <x:v>resource-viewer,api</x:v>
       </x:c>
       <x:c r="M33" t="str">
         <x:v>QA</x:v>
@@ -2731,19 +2723,19 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="str">
-        <x:v>TC-UI-RVW-001</x:v>
+        <x:v>TC-RVW-API-016</x:v>
       </x:c>
       <x:c r="B34" t="str">
-        <x:v>REQ-RVW-UI</x:v>
+        <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="C34" t="str">
-        <x:v>AC-01</x:v>
+        <x:v>AC-10</x:v>
       </x:c>
       <x:c r="D34" t="str">
-        <x:v>UI — wolf sidebar «Відстеження ресурсів»</x:v>
+        <x:v>API — отримувачі ПМ 414 / СБС / Інші</x:v>
       </x:c>
       <x:c r="E34" t="str">
-        <x:v>Мета: Після логіну wolf бачить пункт sidebar і відкриває журнал.</x:v>
+        <x:v>Мета: unitsOther=Інші включає типовий UNIT; unit414Pm і СБС без ПМ — ні.</x:v>
       </x:c>
       <x:c r="F34" t="str">
         <x:v>HIGH</x:v>
@@ -2758,13 +2750,13 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J34" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging.</x:v>
       </x:c>
       <x:c r="K34" t="str">
-        <x:v>h1 «Журнал переміщень ресурсів»</x:v>
+        <x:v>немає relocation</x:v>
       </x:c>
       <x:c r="L34" t="str">
-        <x:v>resource-viewer,ui,smoke</x:v>
+        <x:v>resource-viewer,api</x:v>
       </x:c>
       <x:c r="M34" t="str">
         <x:v>QA</x:v>
@@ -2780,25 +2772,25 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="str">
-        <x:v>TC-UI-RVW-002</x:v>
+        <x:v>TC-RVW-API-017</x:v>
       </x:c>
       <x:c r="B35" t="str">
-        <x:v>REQ-RVW-UI</x:v>
+        <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="C35" t="str">
-        <x:v>AC-02</x:v>
+        <x:v>AC-10</x:v>
       </x:c>
       <x:c r="D35" t="str">
-        <x:v>UI — пошук: таблиця + Сумарно переміщено</x:v>
+        <x:v>API — receiverIds AND unit414Pm</x:v>
       </x:c>
       <x:c r="E35" t="str">
-        <x:v>Мета: Після Шукати картка sum збігається з API; у таблиці product/ingredient рядки.</x:v>
+        <x:v>Мета: Перетин явного receiverIds з ПМ 414 порожній, якщо UNIT поза ПМ.</x:v>
       </x:c>
       <x:c r="F35" t="str">
         <x:v>HIGH</x:v>
       </x:c>
       <x:c r="G35" t="str">
-        <x:v>CRITICAL</x:v>
+        <x:v>MAJOR</x:v>
       </x:c>
       <x:c r="H35" t="str">
         <x:v>ACTIVE</x:v>
@@ -2807,13 +2799,13 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J35" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging. @Admin підготував техкарти PRODUCTION + stock на OWNER_1 storage; receiver = UNIT storage. Видано Product зі Alcohol (self-produced).</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging.</x:v>
       </x:c>
       <x:c r="K35" t="str">
-        <x:v>є product і ingredient рядки для Alcohol</x:v>
+        <x:v>content=[]; sum=0</x:v>
       </x:c>
       <x:c r="L35" t="str">
-        <x:v>resource-viewer,ui</x:v>
+        <x:v>resource-viewer,api</x:v>
       </x:c>
       <x:c r="M35" t="str">
         <x:v>QA</x:v>
@@ -2829,19 +2821,19 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="str">
-        <x:v>TC-RVW-BOM-035</x:v>
+        <x:v>TC-RVW-API-018</x:v>
       </x:c>
       <x:c r="B36" t="str">
-        <x:v>REQ-RVW-BOM</x:v>
+        <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="C36" t="str">
-        <x:v>AC-15</x:v>
+        <x:v>AC-11</x:v>
       </x:c>
       <x:c r="D36" t="str">
-        <x:v>BOM — до першої tech map ресурс атомарний</x:v>
+        <x:v>API — category-only не дублює переміщення продукту та компонента</x:v>
       </x:c>
       <x:c r="E36" t="str">
-        <x:v>Мета: Якщо на момент переміщення не існувало жодної tech map, пізніше створена карта не змінює історичний склад.</x:v>
+        <x:v>Мета: Один рядок journal за relocationId, коли продукт і компонент належать до вибраної категорії; найнижчий компонент містить groupedFrom, а sum не подвоюється.</x:v>
       </x:c>
       <x:c r="F36" t="str">
         <x:v>HIGH</x:v>
@@ -2856,10 +2848,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J36" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging. @Admin підготував техкарти PRODUCTION + stock на OWNER_1 storage; receiver = UNIT storage.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging.</x:v>
       </x:c>
       <x:c r="K36" t="str">
-        <x:v>Component відсутній; Product лишається атомарним, isProduct=false</x:v>
+        <x:v>Передача продукту A присутня рівно один раз за relocationId; показано компонент Б, groupedFrom містить продукт A, а підсумок компонента не подвоєний.</x:v>
       </x:c>
       <x:c r="L36" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -2867,30 +2859,30 @@
       <x:c r="M36" t="str">
         <x:v>QA</x:v>
       </x:c>
-      <x:c r="N36"/>
+      <x:c r="N36" t="str"/>
       <x:c r="O36" t="str">
         <x:v>ResourceViewer</x:v>
       </x:c>
       <x:c r="P36" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="Q36"/>
+      <x:c r="Q36" t="str"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="str">
-        <x:v>TC-RVW-BOM-036</x:v>
+        <x:v>TC-RVW-API-019</x:v>
       </x:c>
       <x:c r="B37" t="str">
-        <x:v>REQ-RVW-BOM</x:v>
+        <x:v>REQ-RVW-FILTER</x:v>
       </x:c>
       <x:c r="C37" t="str">
-        <x:v>AC-15</x:v>
+        <x:v>AC-12</x:v>
       </x:c>
       <x:c r="D37" t="str">
-        <x:v>BOM — зовнішня партія до першої tech map атомарна</x:v>
+        <x:v>API — явно вибрані готовий виріб і напівфабрикат не згортаються</x:v>
       </x:c>
       <x:c r="E37" t="str">
-        <x:v>Мета: Зовнішньо отримана партія, переміщена до появи першої tech map, лишається атомарною; пізніше створена карта не змінює історичний склад.</x:v>
+        <x:v>Мета: resourceIds=[A,Б] повертає декомпозицію A через Б та окреме представлення явно вибраного A; суми містять обидва рівні, groupedFrom порожній.</x:v>
       </x:c>
       <x:c r="F37" t="str">
         <x:v>HIGH</x:v>
@@ -2905,10 +2897,10 @@
         <x:v>FUNCTIONAL</x:v>
       </x:c>
       <x:c r="J37" t="str">
-        <x:v>@ResourceViewer (wolf) залогінений. Середовище dev/staging. @Admin підготував техкарти PRODUCTION + stock на OWNER_1 storage; receiver = UNIT storage.</x:v>
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging.</x:v>
       </x:c>
       <x:c r="K37" t="str">
-        <x:v>Один атомарний рядок Product, isProduct=false</x:v>
+        <x:v>A та Б присутні з коректними сумами; groupedFrom порожній</x:v>
       </x:c>
       <x:c r="L37" t="str">
         <x:v>resource-viewer,api</x:v>
@@ -2916,14 +2908,406 @@
       <x:c r="M37" t="str">
         <x:v>QA</x:v>
       </x:c>
-      <x:c r="N37"/>
+      <x:c r="N37" t="str"/>
       <x:c r="O37" t="str">
         <x:v>ResourceViewer</x:v>
       </x:c>
       <x:c r="P37" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="Q37"/>
+      <x:c r="Q37" t="str"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>TC-RVW-API-021</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>REQ-RVW-FILTER</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>AC-13</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>API — category-only групування за найвищим компонентом</x:v>
+      </x:c>
+      <x:c r="E38" t="str">
+        <x:v>Мета: groupByLowestComponents=false залишає A, згортає Б у groupedFrom та не дублює relocation.</x:v>
+      </x:c>
+      <x:c r="F38" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="G38" t="str">
+        <x:v>CRITICAL</x:v>
+      </x:c>
+      <x:c r="H38" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="I38" t="str">
+        <x:v>FUNCTIONAL</x:v>
+      </x:c>
+      <x:c r="J38" t="str">
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging.</x:v>
+      </x:c>
+      <x:c r="K38" t="str">
+        <x:v>Є A з кількістю relocation; Б окремо відсутній</x:v>
+      </x:c>
+      <x:c r="L38" t="str">
+        <x:v>resource-viewer,api</x:v>
+      </x:c>
+      <x:c r="M38" t="str">
+        <x:v>QA</x:v>
+      </x:c>
+      <x:c r="N38" t="str"/>
+      <x:c r="O38" t="str">
+        <x:v>ResourceViewer</x:v>
+      </x:c>
+      <x:c r="P38" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="Q38" t="str"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>TC-RVW-API-020</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>REQ-RVW-FILTER</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>AC-06</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>API — Excel export</x:v>
+      </x:c>
+      <x:c r="E39" t="str">
+        <x:v>Мета: Валідний фільтр → .xlsx непорожній; guard → порожнє тіло.</x:v>
+      </x:c>
+      <x:c r="F39" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="G39" t="str">
+        <x:v>CRITICAL</x:v>
+      </x:c>
+      <x:c r="H39" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="I39" t="str">
+        <x:v>FUNCTIONAL</x:v>
+      </x:c>
+      <x:c r="J39" t="str">
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging.</x:v>
+      </x:c>
+      <x:c r="K39" t="str">
+        <x:v>200; body порожній</x:v>
+      </x:c>
+      <x:c r="L39" t="str">
+        <x:v>resource-viewer,api</x:v>
+      </x:c>
+      <x:c r="M39" t="str">
+        <x:v>QA</x:v>
+      </x:c>
+      <x:c r="N39" t="str"/>
+      <x:c r="O39" t="str">
+        <x:v>ResourceViewer</x:v>
+      </x:c>
+      <x:c r="P39" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="Q39" t="str"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>TC-UI-RES-AC-001</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>REQ-RVW-UI</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>AC-03</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>UI — autocomplete з фільтром категорії</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>Мета: Категорія A: autocomplete показує ресурс A, не B.</x:v>
+      </x:c>
+      <x:c r="F40" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="G40" t="str">
+        <x:v>MAJOR</x:v>
+      </x:c>
+      <x:c r="H40" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="I40" t="str">
+        <x:v>FUNCTIONAL</x:v>
+      </x:c>
+      <x:c r="J40" t="str">
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging.</x:v>
+      </x:c>
+      <x:c r="K40" t="str">
+        <x:v>є A і B</x:v>
+      </x:c>
+      <x:c r="L40" t="str">
+        <x:v>resource-viewer,ui</x:v>
+      </x:c>
+      <x:c r="M40" t="str">
+        <x:v>QA</x:v>
+      </x:c>
+      <x:c r="N40" t="str"/>
+      <x:c r="O40" t="str">
+        <x:v>ResourceViewer</x:v>
+      </x:c>
+      <x:c r="P40" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="Q40" t="str"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>TC-UI-RVW-001</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>REQ-RVW-UI</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>AC-01</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>UI — Resource Viewer sidebar «Відстеження ресурсів»</x:v>
+      </x:c>
+      <x:c r="E41" t="str">
+        <x:v>Мета: Після логіну динамічний Resource Viewer бачить пункт sidebar і відкриває журнал.</x:v>
+      </x:c>
+      <x:c r="F41" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="G41" t="str">
+        <x:v>CRITICAL</x:v>
+      </x:c>
+      <x:c r="H41" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="I41" t="str">
+        <x:v>FUNCTIONAL</x:v>
+      </x:c>
+      <x:c r="J41" t="str">
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging.</x:v>
+      </x:c>
+      <x:c r="K41" t="str">
+        <x:v>h1 «Журнал переміщень ресурсів»</x:v>
+      </x:c>
+      <x:c r="L41" t="str">
+        <x:v>resource-viewer,ui,smoke</x:v>
+      </x:c>
+      <x:c r="M41" t="str">
+        <x:v>QA</x:v>
+      </x:c>
+      <x:c r="N41" t="str"/>
+      <x:c r="O41" t="str">
+        <x:v>ResourceViewer</x:v>
+      </x:c>
+      <x:c r="P41" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="Q41" t="str"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>TC-UI-RVW-002</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>REQ-RVW-UI</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>AC-02</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>UI — пошук: таблиця + Сумарно переміщено</x:v>
+      </x:c>
+      <x:c r="E42" t="str">
+        <x:v>Мета: Після Шукати картка sum збігається з API; у таблиці product/ingredient рядки.</x:v>
+      </x:c>
+      <x:c r="F42" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="G42" t="str">
+        <x:v>CRITICAL</x:v>
+      </x:c>
+      <x:c r="H42" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="I42" t="str">
+        <x:v>FUNCTIONAL</x:v>
+      </x:c>
+      <x:c r="J42" t="str">
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging. @Admin підготував tech maps PRODUCTION і stock на дочірній локації TSUK_PARENT_UNITS; receiver — локація поза TSUK_PARENT_UNITS. Видано Product зі Alcohol (self-produced).</x:v>
+      </x:c>
+      <x:c r="K42" t="str">
+        <x:v>є product і ingredient рядки для Alcohol</x:v>
+      </x:c>
+      <x:c r="L42" t="str">
+        <x:v>resource-viewer,ui</x:v>
+      </x:c>
+      <x:c r="M42" t="str">
+        <x:v>QA</x:v>
+      </x:c>
+      <x:c r="N42" t="str"/>
+      <x:c r="O42" t="str">
+        <x:v>ResourceViewer</x:v>
+      </x:c>
+      <x:c r="P42" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="Q42" t="str"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>TC-UI-RVW-003</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>REQ-RVW-UI</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>AC-04</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>UI — Excel export поточного результату</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>Мета: Поточні resourceIds і receiverIds передаються в export; завантажений XLSX непорожній.</x:v>
+      </x:c>
+      <x:c r="F43" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="G43" t="str">
+        <x:v>CRITICAL</x:v>
+      </x:c>
+      <x:c r="H43" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="I43" t="str">
+        <x:v>FUNCTIONAL</x:v>
+      </x:c>
+      <x:c r="J43" t="str">
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging.</x:v>
+      </x:c>
+      <x:c r="K43" t="str">
+        <x:v>Завантажено непорожній .xlsx</x:v>
+      </x:c>
+      <x:c r="L43" t="str">
+        <x:v>resource-viewer,ui</x:v>
+      </x:c>
+      <x:c r="M43" t="str">
+        <x:v>QA</x:v>
+      </x:c>
+      <x:c r="N43" t="str"/>
+      <x:c r="O43" t="str">
+        <x:v>ResourceViewer</x:v>
+      </x:c>
+      <x:c r="P43" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="Q43" t="str"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>TC-UI-RVW-004</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>REQ-RVW-UI</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>AC-05</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>UI — category-only групує продукт і компонент в один рядок</x:v>
+      </x:c>
+      <x:c r="E44" t="str">
+        <x:v>Мета: Перемикач доступний і checked; один relocation-row має позначку «Згруповано».</x:v>
+      </x:c>
+      <x:c r="F44" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="G44" t="str">
+        <x:v>CRITICAL</x:v>
+      </x:c>
+      <x:c r="H44" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="I44" t="str">
+        <x:v>FUNCTIONAL</x:v>
+      </x:c>
+      <x:c r="J44" t="str">
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging.</x:v>
+      </x:c>
+      <x:c r="K44" t="str">
+        <x:v>Один рядок A; є Б і «Згруповано»</x:v>
+      </x:c>
+      <x:c r="L44" t="str">
+        <x:v>resource-viewer,ui</x:v>
+      </x:c>
+      <x:c r="M44" t="str">
+        <x:v>QA</x:v>
+      </x:c>
+      <x:c r="N44" t="str"/>
+      <x:c r="O44" t="str">
+        <x:v>ResourceViewer</x:v>
+      </x:c>
+      <x:c r="P44" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="Q44" t="str"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>TC-UI-RVW-005</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>REQ-RVW-UI</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>AC-06</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>UI — явно вибрані готовий виріб і напівфабрикат показані окремо</x:v>
+      </x:c>
+      <x:c r="E45" t="str">
+        <x:v>Мета: Після resourceIds=[A,Б] grouping disabled; UI показує обидві декомпозиції без «Згруповано».</x:v>
+      </x:c>
+      <x:c r="F45" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="G45" t="str">
+        <x:v>CRITICAL</x:v>
+      </x:c>
+      <x:c r="H45" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="I45" t="str">
+        <x:v>FUNCTIONAL</x:v>
+      </x:c>
+      <x:c r="J45" t="str">
+        <x:v>Динамічний @ResourceViewer з глобальною роллю «Відстеження ресурсів» залогінений. Середовище dev/staging.</x:v>
+      </x:c>
+      <x:c r="K45" t="str">
+        <x:v>Два логічні рядки relocation; немає «Згруповано»</x:v>
+      </x:c>
+      <x:c r="L45" t="str">
+        <x:v>resource-viewer,ui</x:v>
+      </x:c>
+      <x:c r="M45" t="str">
+        <x:v>QA</x:v>
+      </x:c>
+      <x:c r="N45" t="str"/>
+      <x:c r="O45" t="str">
+        <x:v>ResourceViewer</x:v>
+      </x:c>
+      <x:c r="P45" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="Q45" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2935,1016 +3319,1008 @@
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">testId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">stepOrder</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">actionText</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">expectedText</x:t>
-        </x:is>
+      <x:c r="A1" t="str">
+        <x:v>testId</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>stepOrder</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>actionText</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>expectedText</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
-        <x:v>TC-RVW-BOM-001</x:v>
+        <x:v>TC-RVW-BOM-037</x:v>
       </x:c>
       <x:c r="B2" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>Створити Alcohol; ensureStock; POST send STORAGE→UNIT</x:v>
+        <x:v>Створити Product←Component@2 та два джерела з протилежними features</x:v>
       </x:c>
       <x:c r="D2" t="str">
-        <x:v>relocationId</x:v>
+        <x:v>Unit-like source в TSUK; warehouse-like source поза TSUK</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
-        <x:v>TC-RVW-BOM-001</x:v>
+        <x:v>TC-RVW-BOM-037</x:v>
       </x:c>
       <x:c r="B3" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>GET /resources-viewer/relocations/sum як wolf</x:v>
+        <x:v>Видати Product з обох джерел одному зовнішньому одержувачу</x:v>
       </x:c>
       <x:c r="D3" t="str">
-        <x:v>amount = sendAmount</x:v>
+        <x:v>2 relocationId</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
-        <x:v>TC-RVW-BOM-001</x:v>
+        <x:v>TC-RVW-BOM-037</x:v>
       </x:c>
       <x:c r="B4" t="str">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>GET journal</x:v>
+        <x:v>GET journal/sums за Component</x:v>
       </x:c>
       <x:c r="D4" t="str">
-        <x:v>рядок isProduct=false; totallyUsage = sendAmount</x:v>
+        <x:v>Є лише TSUK relocation; Component = amount×2</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
-        <x:v>TC-RVW-BOM-002</x:v>
+        <x:v>TC-RVW-BOM-001</x:v>
       </x:c>
       <x:c r="B5" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>Tech map Product←Alcohol@2; produce; send batch isProduced=true</x:v>
+        <x:v>Створити Alcohol; ensureStock; POST send з TSUK до зовнішньої структури</x:v>
       </x:c>
       <x:c r="D5" t="str">
-        <x:v>setup</x:v>
+        <x:v>relocationId</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str">
-        <x:v>TC-RVW-BOM-002</x:v>
+        <x:v>TC-RVW-BOM-001</x:v>
       </x:c>
       <x:c r="B6" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C6" t="str">
-        <x:v>GET sum/journal як wolf</x:v>
+        <x:v>GET /resources-viewer/relocations/sum як Resource Viewer</x:v>
       </x:c>
       <x:c r="D6" t="str">
-        <x:v>Alcohol amount = relocate×2; isProduct=true</x:v>
+        <x:v>amount = sendAmount</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
-        <x:v>TC-RVW-BOM-003</x:v>
+        <x:v>TC-RVW-BOM-001</x:v>
       </x:c>
       <x:c r="B7" t="str">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C7" t="str">
-        <x:v>Tech map; seed external batch; send isProduced=false</x:v>
+        <x:v>GET journal</x:v>
       </x:c>
       <x:c r="D7" t="str">
-        <x:v>setup</x:v>
+        <x:v>рядок isProduct=false; totallyUsage = sendAmount</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str">
-        <x:v>TC-RVW-BOM-003</x:v>
+        <x:v>TC-RVW-BOM-002</x:v>
       </x:c>
       <x:c r="B8" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C8" t="str">
-        <x:v>GET journal/sum</x:v>
+        <x:v>Tech map Product←Alcohol@2; produce; send batch isProduced=true</x:v>
       </x:c>
       <x:c r="D8" t="str">
-        <x:v>Alcohol = relocate × usage з tech map</x:v>
+        <x:v>setup</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="str">
-        <x:v>TC-RVW-BOM-004</x:v>
+        <x:v>TC-RVW-BOM-002</x:v>
       </x:c>
       <x:c r="B9" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C9" t="str">
-        <x:v>Produce 5 + seed 5; send 10 з двома партіями</x:v>
+        <x:v>GET sum/journal як Resource Viewer</x:v>
       </x:c>
       <x:c r="D9" t="str">
-        <x:v>relocationId</x:v>
+        <x:v>Alcohol amount = relocate×2; isProduct=true</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="str">
-        <x:v>TC-RVW-BOM-004</x:v>
+        <x:v>TC-RVW-BOM-003</x:v>
       </x:c>
       <x:c r="B10" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C10" t="str">
-        <x:v>GET sum</x:v>
+        <x:v>Створити tech map з fixed input і default/non-default alternatives</x:v>
       </x:c>
       <x:c r="D10" t="str">
-        <x:v>Alcohol = 10 × usage</x:v>
+        <x:v>Tech map існує до переміщення</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="str">
-        <x:v>TC-RVW-BOM-010</x:v>
+        <x:v>TC-RVW-BOM-003</x:v>
       </x:c>
       <x:c r="B11" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C11" t="str">
-        <x:v>Produce+relocate depth1</x:v>
+        <x:v>Seed external batch; send isProduced=false</x:v>
       </x:c>
       <x:c r="D11" t="str">
-        <x:v>sum = relocate × alcPerUnit</x:v>
+        <x:v>relocationId</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="str">
-        <x:v>TC-RVW-BOM-011</x:v>
+        <x:v>TC-RVW-BOM-003</x:v>
       </x:c>
       <x:c r="B12" t="str">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C12" t="str">
-        <x:v>Chain SF→Product; relocate Product</x:v>
+        <x:v>GET journal/sum</x:v>
       </x:c>
       <x:c r="D12" t="str">
-        <x:v>sum = relocate×semi×alc</x:v>
+        <x:v>Fixed і default alternative розраховані; non-default = 0</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
-        <x:v>TC-RVW-BOM-012</x:v>
+        <x:v>TC-RVW-BOM-004</x:v>
       </x:c>
       <x:c r="B13" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C13" t="str">
-        <x:v>3-level chain; relocate</x:v>
+        <x:v>Produce 5 з non-default alternative; seed external 5</x:v>
       </x:c>
       <x:c r="D13" t="str">
-        <x:v>sum = добуток коефіцієнтів</x:v>
+        <x:v>Дві партії різного походження</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
-        <x:v>TC-RVW-BOM-020</x:v>
+        <x:v>TC-RVW-BOM-004</x:v>
       </x:c>
       <x:c r="B14" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C14" t="str">
-        <x:v>Nested + direct issue</x:v>
+        <x:v>Send 10 з produced=true та produced=false batches</x:v>
       </x:c>
       <x:c r="D14" t="str">
-        <x:v>sum = nested + direct</x:v>
+        <x:v>relocationId</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
-        <x:v>TC-RVW-BOM-021</x:v>
+        <x:v>TC-RVW-BOM-004</x:v>
       </x:c>
       <x:c r="B15" t="str">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C15" t="str">
-        <x:v>Дві видачі; GET journal/sum для Semi</x:v>
+        <x:v>GET journal/sum</x:v>
       </x:c>
       <x:c r="D15" t="str">
-        <x:v>обидва рядки; sum = direct + nested</x:v>
+        <x:v>Produced використовує non-default; external використовує default; fixed враховано для всіх 10</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
-        <x:v>TC-RVW-BOM-022</x:v>
+        <x:v>TC-RVW-BOM-010</x:v>
       </x:c>
       <x:c r="B16" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C16" t="str">
-        <x:v>Send unrelated; GET sum/journal Alcohol</x:v>
+        <x:v>Produce+relocate depth1</x:v>
       </x:c>
       <x:c r="D16" t="str">
-        <x:v>sum=0; relocation відсутній</x:v>
+        <x:v>sum = relocate × alcPerUnit</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
-        <x:v>TC-RVW-ALT-001</x:v>
+        <x:v>TC-RVW-BOM-011</x:v>
       </x:c>
       <x:c r="B17" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C17" t="str">
-        <x:v>Tech map з alt group; produce з non-default alt</x:v>
+        <x:v>Chain SF→Product; relocate Product</x:v>
       </x:c>
       <x:c r="D17" t="str">
-        <x:v>batch</x:v>
+        <x:v>sum = relocate×semi×alc</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
-        <x:v>TC-RVW-ALT-001</x:v>
+        <x:v>TC-RVW-BOM-012</x:v>
       </x:c>
       <x:c r="B18" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C18" t="str">
-        <x:v>Relocate; GET sum для alt resource</x:v>
+        <x:v>3-level chain; relocate</x:v>
       </x:c>
       <x:c r="D18" t="str">
-        <x:v>amount = usage×relocate</x:v>
+        <x:v>sum = добуток коефіцієнтів</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="str">
-        <x:v>TC-RVW-ALT-002</x:v>
+        <x:v>TC-RVW-BOM-020</x:v>
       </x:c>
       <x:c r="B19" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C19" t="str">
-        <x:v>Produce з default alt; relocate</x:v>
+        <x:v>Nested + direct issue</x:v>
       </x:c>
       <x:c r="D19" t="str">
-        <x:v>batch</x:v>
+        <x:v>sum = nested + direct</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="str">
-        <x:v>TC-RVW-ALT-002</x:v>
+        <x:v>TC-RVW-BOM-021</x:v>
       </x:c>
       <x:c r="B20" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C20" t="str">
-        <x:v>GET sum для default alt resource</x:v>
+        <x:v>Дві видачі; GET journal/sum для Semi</x:v>
       </x:c>
       <x:c r="D20" t="str">
-        <x:v>amount коректний</x:v>
+        <x:v>обидва рядки; sum = direct + nested</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="str">
-        <x:v>TC-RVW-BOM-030</x:v>
+        <x:v>TC-RVW-BOM-022</x:v>
       </x:c>
       <x:c r="B21" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C21" t="str">
-        <x:v>Produce 4@usage2 + 6@usage4 з shared batch</x:v>
+        <x:v>Send unrelated; GET sum/journal Alcohol</x:v>
       </x:c>
       <x:c r="D21" t="str">
-        <x:v>setup</x:v>
+        <x:v>sum=0; relocation відсутній</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
-        <x:v>TC-RVW-BOM-030</x:v>
+        <x:v>TC-RVW-ALT-001</x:v>
       </x:c>
       <x:c r="B22" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>Relocate 10; GET sum</x:v>
+        <x:v>Tech map з alt group; produce з non-default alt</x:v>
       </x:c>
       <x:c r="D22" t="str">
-        <x:v>Alcohol = 32 (per-unit 3.2)</x:v>
+        <x:v>batch</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
-        <x:v>TC-RVW-BOM-031</x:v>
+        <x:v>TC-RVW-ALT-001</x:v>
       </x:c>
       <x:c r="B23" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C23" t="str">
-        <x:v>Tech map; ensureStock Product; send без batch</x:v>
+        <x:v>Relocate; GET sum для alt resource</x:v>
       </x:c>
       <x:c r="D23" t="str">
-        <x:v>relocationId</x:v>
+        <x:v>amount = usage×relocate</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str">
-        <x:v>TC-RVW-BOM-031</x:v>
+        <x:v>TC-RVW-ALT-002</x:v>
       </x:c>
       <x:c r="B24" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C24" t="str">
-        <x:v>GET sum/journal</x:v>
+        <x:v>Produce з default alt; relocate</x:v>
       </x:c>
       <x:c r="D24" t="str">
-        <x:v>Alcohol = relocate × usage</x:v>
+        <x:v>batch</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="str">
-        <x:v>TC-RVW-BOM-032</x:v>
+        <x:v>TC-RVW-ALT-002</x:v>
       </x:c>
       <x:c r="B25" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C25" t="str">
-        <x:v>Дві техкарти V1@2 потім V2@5; external sends date=yesterday і tomorrow</x:v>
+        <x:v>GET sum для default alt resource</x:v>
       </x:c>
       <x:c r="D25" t="str">
-        <x:v>2 relocationId</x:v>
+        <x:v>amount коректний</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str">
-        <x:v>TC-RVW-BOM-032</x:v>
+        <x:v>TC-RVW-BOM-030</x:v>
       </x:c>
       <x:c r="B26" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>GET journal</x:v>
+        <x:v>За однією tech map створити 4@usage2, потім 6@usage4 з shared batch</x:v>
       </x:c>
       <x:c r="D26" t="str">
-        <x:v>past×2; future×5</x:v>
+        <x:v>Два валідні production records</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="str">
-        <x:v>TC-RVW-BOM-033</x:v>
+        <x:v>TC-RVW-BOM-030</x:v>
       </x:c>
       <x:c r="B27" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>Дві циклічні tech maps; send A без production</x:v>
+        <x:v>Relocate 10; GET sum</x:v>
       </x:c>
       <x:c r="D27" t="str">
-        <x:v>relocationId</x:v>
+        <x:v>Alcohol = 40 за останнім usage4</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="str">
-        <x:v>TC-RVW-BOM-033</x:v>
+        <x:v>TC-RVW-BOM-031</x:v>
       </x:c>
       <x:c r="B28" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>GET journal resourceIds=[B]</x:v>
+        <x:v>Tech map; ensureStock Product; send без batch</x:v>
       </x:c>
       <x:c r="D28" t="str">
-        <x:v>totallyUsage = amount; без дубля</x:v>
+        <x:v>relocationId</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="str">
-        <x:v>TC-RVW-BOM-034</x:v>
+        <x:v>TC-RVW-BOM-031</x:v>
       </x:c>
       <x:c r="B29" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>Produce+relocate Product; UPDATE amount вниз</x:v>
+        <x:v>GET sum/journal</x:v>
       </x:c>
       <x:c r="D29" t="str">
-        <x:v>drift</x:v>
+        <x:v>Alcohol = relocate × usage</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
-        <x:v>TC-RVW-BOM-034</x:v>
+        <x:v>TC-RVW-BOM-032</x:v>
       </x:c>
       <x:c r="B30" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>GET sum/journal Alcohol</x:v>
+        <x:v>Backdate V1@2 і V2@5; виконати переміщення між датами карт та після V2</x:v>
       </x:c>
       <x:c r="D30" t="str">
-        <x:v>amount×usage; не повний producedQty×usage</x:v>
+        <x:v>2 relocationId</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str">
-        <x:v>TC-RVW-001</x:v>
+        <x:v>TC-RVW-BOM-032</x:v>
       </x:c>
       <x:c r="B31" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C31" t="str">
-        <x:v>Створити 8 ресурсів з префіксами</x:v>
+        <x:v>GET journal</x:v>
       </x:c>
       <x:c r="D31" t="str">
-        <x:v>ids</x:v>
+        <x:v>Перше переміщення = amount×2; друге = amount×5</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="str">
-        <x:v>TC-RVW-001</x:v>
+        <x:v>TC-RVW-BOM-032</x:v>
       </x:c>
       <x:c r="B32" t="str">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C32" t="str">
-        <x:v>GET /resources-viewer/relocations?resourceIds=…&amp;receiverIds=UNIT</x:v>
+        <x:v>Деактивувати V1/V2, створити V3@9 після переміщень; повторити GET</x:v>
       </x:c>
       <x:c r="D32" t="str">
-        <x:v>HTTP 200</x:v>
+        <x:v>Обидва історичні склади не змінилися</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="str">
-        <x:v>TC-RVW-001</x:v>
+        <x:v>TC-RVW-BOM-033</x:v>
       </x:c>
       <x:c r="B33" t="str">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C33" t="str">
-        <x:v>Перевірити sums містить усі ids з amount=0 і порядок ASC</x:v>
+        <x:v>Три циклічні tech maps; send A без production</x:v>
       </x:c>
       <x:c r="D33" t="str">
-        <x:v>До фіксу: sums=[]; після фіксу: 111→…→їжа, нулі</x:v>
+        <x:v>relocationId</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="str">
-        <x:v>TC-RVW-API-001</x:v>
+        <x:v>TC-RVW-BOM-033</x:v>
       </x:c>
       <x:c r="B34" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C34" t="str">
-        <x:v>GET /storages/names/my-units як wolf</x:v>
+        <x:v>GET journal resourceIds=[A,B,C]</x:v>
       </x:c>
       <x:c r="D34" t="str">
-        <x:v>HTTP 200</x:v>
+        <x:v>Ingredients містять A, B і C по одному разу; повторного A немає</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="str">
-        <x:v>TC-RVW-API-001</x:v>
+        <x:v>TC-RVW-BOM-034</x:v>
       </x:c>
       <x:c r="B35" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C35" t="str">
-        <x:v>Жоден type=UNIT</x:v>
+        <x:v>Produce+relocate Product; UPDATE amount вниз</x:v>
       </x:c>
       <x:c r="D35" t="str">
-        <x:v>OK</x:v>
+        <x:v>drift</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="str">
-        <x:v>TC-RVW-API-002</x:v>
+        <x:v>TC-RVW-BOM-034</x:v>
       </x:c>
       <x:c r="B36" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C36" t="str">
-        <x:v>ADMIN: send STORAGE/PRODUCTION→UNIT і UNIT→UNIT</x:v>
+        <x:v>GET sum/journal Alcohol</x:v>
       </x:c>
       <x:c r="D36" t="str">
-        <x:v>2 relocationId</x:v>
+        <x:v>amount×usage; не повний producedQty×usage</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="str">
-        <x:v>TC-RVW-API-002</x:v>
+        <x:v>TC-RVW-BOM-035</x:v>
       </x:c>
       <x:c r="B37" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C37" t="str">
-        <x:v>GET /resources-viewer/relocations як wolf (receiverIds=UNIT)</x:v>
+        <x:v>Створити inventory stock Product і перемістити його до появи tech map</x:v>
       </x:c>
       <x:c r="D37" t="str">
-        <x:v>HTTP 200</x:v>
+        <x:v>relocationId</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="str">
-        <x:v>TC-RVW-API-002</x:v>
+        <x:v>TC-RVW-BOM-035</x:v>
       </x:c>
       <x:c r="B38" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C38" t="str">
-        <x:v>Перевірити content</x:v>
+        <x:v>Після переміщення створити tech map Product←Component</x:v>
       </x:c>
       <x:c r="D38" t="str">
-        <x:v>Є STORAGE/PRODUCTION→UNIT; немає UNIT→UNIT</x:v>
+        <x:v>Tech map створена пізніше</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="str">
-        <x:v>TC-RVW-API-003</x:v>
+        <x:v>TC-RVW-BOM-035</x:v>
       </x:c>
       <x:c r="B39" t="str">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C39" t="str">
-        <x:v>Send UNIT→CREW tracked resource (ADMIN arrange)</x:v>
+        <x:v>GET journal/sum</x:v>
       </x:c>
       <x:c r="D39" t="str">
-        <x:v>relocation</x:v>
+        <x:v>Component відсутній; Product лишається атомарним, isProduct=false</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="str">
-        <x:v>TC-RVW-API-003</x:v>
+        <x:v>TC-RVW-BOM-036</x:v>
       </x:c>
       <x:c r="B40" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C40" t="str">
-        <x:v>GET /relocations як wolf → sums</x:v>
+        <x:v>Отримати Product зовнішньою партією та перемістити її до появи tech map</x:v>
       </x:c>
       <x:c r="D40" t="str">
-        <x:v>amount=0</x:v>
+        <x:v>relocationId; isProduced=false</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="str">
-        <x:v>TC-RVW-API-010</x:v>
+        <x:v>TC-RVW-BOM-036</x:v>
       </x:c>
       <x:c r="B41" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C41" t="str">
-        <x:v>Product з inputs у cat A і cat B; relocate</x:v>
+        <x:v>Після переміщення створити tech map Product←Component</x:v>
       </x:c>
       <x:c r="D41" t="str">
-        <x:v>setup</x:v>
+        <x:v>Tech map створена пізніше</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" t="str">
-        <x:v>TC-RVW-API-010</x:v>
+        <x:v>TC-RVW-BOM-036</x:v>
       </x:c>
       <x:c r="B42" t="str">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C42" t="str">
-        <x:v>GET sum?categoryIds=A</x:v>
+        <x:v>GET journal/sum за Component</x:v>
       </x:c>
       <x:c r="D42" t="str">
-        <x:v>A у sum; B відсутній</x:v>
+        <x:v>Relocation відсутній; Component amount=0</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" t="str">
-        <x:v>TC-RVW-API-011</x:v>
+        <x:v>TC-RVW-BOM-036</x:v>
       </x:c>
       <x:c r="B43" t="str">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C43" t="str">
-        <x:v>Alcohol з property Постачальник=Match; produce+relocate</x:v>
+        <x:v>GET journal за Product</x:v>
       </x:c>
       <x:c r="D43" t="str">
-        <x:v>setup</x:v>
+        <x:v>Один атомарний рядок Product, isProduct=false</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="str">
-        <x:v>TC-RVW-API-011</x:v>
+        <x:v>TC-RVW-001</x:v>
       </x:c>
       <x:c r="B44" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C44" t="str">
-        <x:v>GET sum supplier=Match / Other</x:v>
+        <x:v>Створити 8 ресурсів з префіксами</x:v>
       </x:c>
       <x:c r="D44" t="str">
-        <x:v>Match&gt;0; Other=0</x:v>
+        <x:v>ids</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" t="str">
-        <x:v>TC-RVW-API-012</x:v>
+        <x:v>TC-RVW-001</x:v>
       </x:c>
       <x:c r="B45" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C45" t="str">
-        <x:v>Send сьогодні; GET з in-range і out-of-range</x:v>
+        <x:v>GET /resources-viewer/relocations?resourceIds=…&amp;receiverIds=UNIT</x:v>
       </x:c>
       <x:c r="D45" t="str">
-        <x:v>in: сума&gt;0; out: 0</x:v>
+        <x:v>HTTP 200</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="str">
-        <x:v>TC-RVW-API-013</x:v>
+        <x:v>TC-RVW-001</x:v>
       </x:c>
       <x:c r="B46" t="str">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C46" t="str">
-        <x:v>GET без resourceIds/categoryIds</x:v>
+        <x:v>Перевірити sums містить усі ids з amount=0 і порядок ASC</x:v>
       </x:c>
       <x:c r="D46" t="str">
-        <x:v>content=[]</x:v>
+        <x:v>До фіксу: sums=[]; після фіксу: 111→…→їжа, нулі</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" t="str">
-        <x:v>TC-RVW-API-013</x:v>
+        <x:v>TC-RVW-API-001</x:v>
       </x:c>
       <x:c r="B47" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C47" t="str">
-        <x:v>GET без receiverIds/unit*</x:v>
+        <x:v>GET /storages/names/my-units як Resource Viewer</x:v>
       </x:c>
       <x:c r="D47" t="str">
-        <x:v>content=[]</x:v>
+        <x:v>HTTP 403 без location grants</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" t="str">
-        <x:v>TC-RVW-API-014</x:v>
+        <x:v>TC-RVW-API-001</x:v>
       </x:c>
       <x:c r="B48" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C48" t="str">
-        <x:v>3+ sends; GET page=0&amp;size=1</x:v>
+        <x:v>GET viewer endpoints з обов'язковими фільтрами</x:v>
       </x:c>
       <x:c r="D48" t="str">
-        <x:v>totalElements≥3; totalPages≥3</x:v>
+        <x:v>HTTP 200 без my-units</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" t="str">
-        <x:v>TC-RVW-API-014</x:v>
+        <x:v>TC-RVW-API-002</x:v>
       </x:c>
       <x:c r="B49" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C49" t="str">
-        <x:v>GET size=100</x:v>
+        <x:v>ADMIN: send з warehouse/production profiles в TSUK назовні і між зовнішніми локаціями</x:v>
       </x:c>
       <x:c r="D49" t="str">
-        <x:v>dates DESC</x:v>
+        <x:v>3 relocationId</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" t="str">
-        <x:v>TC-RVW-API-015</x:v>
+        <x:v>TC-RVW-API-002</x:v>
       </x:c>
       <x:c r="B50" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C50" t="str">
-        <x:v>ADMIN send STORAGE→UNIT; GET UI states</x:v>
+        <x:v>GET /resources-viewer/relocations як Resource Viewer</x:v>
       </x:c>
       <x:c r="D50" t="str">
-        <x:v>рядок і sum&gt;0</x:v>
+        <x:v>HTTP 200</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" t="str">
-        <x:v>TC-RVW-API-015</x:v>
+        <x:v>TC-RVW-API-002</x:v>
       </x:c>
       <x:c r="B51" t="str">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C51" t="str">
-        <x:v>GET states=CANCELLED|RETURNED</x:v>
+        <x:v>Перевірити content і sums</x:v>
       </x:c>
       <x:c r="D51" t="str">
-        <x:v>немає relocationId</x:v>
+        <x:v>Є два TSUK→outside; outside→outside відсутнє</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" t="str">
-        <x:v>TC-RVW-API-015</x:v>
+        <x:v>TC-RVW-API-003</x:v>
       </x:c>
       <x:c r="B52" t="str">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C52" t="str">
-        <x:v>(опц.) RETURNED; GET UI states + end bust-cache</x:v>
+        <x:v>Send зовнішня location→CREW/FLY_POINT (ADMIN arrange)</x:v>
       </x:c>
       <x:c r="D52" t="str">
-        <x:v>немає рядка; sum≈0</x:v>
+        <x:v>relocation</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" t="str">
-        <x:v>TC-RVW-API-016</x:v>
+        <x:v>TC-RVW-API-003</x:v>
       </x:c>
       <x:c r="B53" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C53" t="str">
-        <x:v>ADMIN send на типовий UNIT</x:v>
+        <x:v>GET /relocations як Resource Viewer → sums</x:v>
       </x:c>
       <x:c r="D53" t="str">
-        <x:v>relocationId</x:v>
+        <x:v>amount=0</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" t="str">
-        <x:v>TC-RVW-API-016</x:v>
+        <x:v>TC-RVW-API-022</x:v>
       </x:c>
       <x:c r="B54" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C54" t="str">
-        <x:v>GET unitsOther=Інші</x:v>
+        <x:v>Створити direct і nested unit-like sources в TSUK</x:v>
       </x:c>
       <x:c r="D54" t="str">
-        <x:v>є relocation; sum=amount</x:v>
+        <x:v>features=[RELOCATIONS, ORDERS]</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" t="str">
-        <x:v>TC-RVW-API-016</x:v>
+        <x:v>TC-RVW-API-022</x:v>
       </x:c>
       <x:c r="B55" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C55" t="str">
-        <x:v>GET unit414Pm / unitSbsExcept414Pm</x:v>
+        <x:v>Створити warehouse-like source поза TSUK і unit-like receiver в TSUK</x:v>
       </x:c>
       <x:c r="D55" t="str">
-        <x:v>немає relocation</x:v>
+        <x:v>Контрприклади готові</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" t="str">
-        <x:v>TC-RVW-API-017</x:v>
+        <x:v>TC-RVW-API-022</x:v>
       </x:c>
       <x:c r="B56" t="str">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C56" t="str">
-        <x:v>Send на UNIT∈Інші</x:v>
+        <x:v>Виконати чотири relocation і GET journal/sums</x:v>
       </x:c>
       <x:c r="D56" t="str">
-        <x:v>setup</x:v>
+        <x:v>Включено лише 2 TSUK→outside</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" t="str">
-        <x:v>TC-RVW-API-017</x:v>
+        <x:v>TC-RVW-API-023</x:v>
       </x:c>
       <x:c r="B57" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C57" t="str">
-        <x:v>GET receiverIds+unit414Pm</x:v>
+        <x:v>Видати один ресурс із unit-like source в TSUK та warehouse-like source поза TSUK</x:v>
       </x:c>
       <x:c r="D57" t="str">
-        <x:v>content=[]; sum=0</x:v>
+        <x:v>2 relocationId</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" t="str">
-        <x:v>TC-RVW-API-018</x:v>
+        <x:v>TC-RVW-API-023</x:v>
       </x:c>
       <x:c r="B58" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C58" t="str">
-        <x:v>Створити продукт A з компонентом Б; обидва ресурси віднести до категорії «Взуття»</x:v>
+        <x:v>GET /resources-viewer/export з resourceIds+receiverIds</x:v>
       </x:c>
       <x:c r="D58" t="str">
-        <x:v>Продукт A, компонент Б і спільна категорія створені</x:v>
+        <x:v>XLSX справний</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" t="str">
-        <x:v>TC-RVW-API-018</x:v>
+        <x:v>TC-RVW-API-023</x:v>
       </x:c>
       <x:c r="B59" t="str">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C59" t="str">
-        <x:v>Виробити продукт A та передати його до вибраного підрозділу</x:v>
+        <x:v>Перевірити XML workbook</x:v>
       </x:c>
       <x:c r="D59" t="str">
-        <x:v>Створено одне фізичне переміщення продукту A</x:v>
+        <x:v>Є TSUK source; outside source відсутнє</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" t="str">
-        <x:v>TC-RVW-API-018</x:v>
+        <x:v>TC-RVW-API-010</x:v>
       </x:c>
       <x:c r="B60" t="str">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C60" t="str">
-        <x:v>Виконати пошук Resource Viewer за категорією «Взуття» та одержувачем</x:v>
+        <x:v>Product з inputs у cat A і cat B; relocate</x:v>
       </x:c>
       <x:c r="D60" t="str">
-        <x:v>relocationId передачі присутній один раз; рядок містить продукт A і компонент Б</x:v>
+        <x:v>setup</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" t="str">
-        <x:v>TC-RVW-API-020</x:v>
+        <x:v>TC-RVW-API-010</x:v>
       </x:c>
       <x:c r="B61" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C61" t="str">
-        <x:v>GET /resources-viewer/export з resourceIds+receiverIds</x:v>
+        <x:v>GET sum?categoryIds=A</x:v>
       </x:c>
       <x:c r="D61" t="str">
-        <x:v>200; Content-Disposition .xlsx; body&gt;0</x:v>
+        <x:v>A у sum; B відсутній</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" t="str">
-        <x:v>TC-RVW-API-020</x:v>
+        <x:v>TC-RVW-API-011</x:v>
       </x:c>
       <x:c r="B62" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C62" t="str">
-        <x:v>GET export без tracking</x:v>
+        <x:v>Alcohol з property Постачальник=Match; produce+relocate</x:v>
       </x:c>
       <x:c r="D62" t="str">
-        <x:v>200; body порожній</x:v>
+        <x:v>setup</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" t="str">
-        <x:v>TC-UI-RES-AC-001</x:v>
+        <x:v>TC-RVW-API-011</x:v>
       </x:c>
       <x:c r="B63" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C63" t="str">
-        <x:v>Відкрити /resources-viewer/relocation</x:v>
+        <x:v>GET sum supplier=Match / Other</x:v>
       </x:c>
       <x:c r="D63" t="str">
-        <x:v>Сторінка завантажена</x:v>
+        <x:v>Match&gt;0; Other=0</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" t="str">
-        <x:v>TC-UI-RES-AC-001</x:v>
+        <x:v>TC-RVW-API-012</x:v>
       </x:c>
       <x:c r="B64" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C64" t="str">
-        <x:v>Обрати категорію A; пошук ресурсів</x:v>
+        <x:v>Send сьогодні; GET з in-range і out-of-range</x:v>
       </x:c>
       <x:c r="D64" t="str">
-        <x:v>є A; немає B</x:v>
+        <x:v>in: сума&gt;0; out: 0</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" t="str">
-        <x:v>TC-UI-RES-AC-001</x:v>
+        <x:v>TC-RVW-API-013</x:v>
       </x:c>
       <x:c r="B65" t="str">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C65" t="str">
-        <x:v>Очистити; пошук знову</x:v>
+        <x:v>GET без resourceIds/categoryIds</x:v>
       </x:c>
       <x:c r="D65" t="str">
-        <x:v>є A і B</x:v>
+        <x:v>content=[]</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" t="str">
-        <x:v>TC-UI-RVW-001</x:v>
+        <x:v>TC-RVW-API-013</x:v>
       </x:c>
       <x:c r="B66" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C66" t="str">
-        <x:v>Увійти як wolf</x:v>
+        <x:v>GET без receiverIds/unit*</x:v>
       </x:c>
       <x:c r="D66" t="str">
-        <x:v>SPA завантажено</x:v>
+        <x:v>content=[]</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" t="str">
-        <x:v>TC-UI-RVW-001</x:v>
+        <x:v>TC-RVW-API-014</x:v>
       </x:c>
       <x:c r="B67" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C67" t="str">
-        <x:v>Перевірити sidebar: «Відстеження ресурсів» видимий</x:v>
+        <x:v>3+ sends; GET page=0&amp;size=1</x:v>
       </x:c>
       <x:c r="D67" t="str">
-        <x:v>link visible</x:v>
+        <x:v>totalElements≥3; totalPages≥3</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" t="str">
-        <x:v>TC-UI-RVW-001</x:v>
+        <x:v>TC-RVW-API-014</x:v>
       </x:c>
       <x:c r="B68" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C68" t="str">
-        <x:v>Відкрити /resources-viewer/relocation</x:v>
+        <x:v>GET size=100</x:v>
       </x:c>
       <x:c r="D68" t="str">
-        <x:v>h1 «Журнал переміщень ресурсів»</x:v>
+        <x:v>dates DESC</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" t="str">
-        <x:v>TC-UI-RVW-002</x:v>
+        <x:v>TC-RVW-API-015</x:v>
       </x:c>
       <x:c r="B69" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C69" t="str">
-        <x:v>Відкрити viewer; обрати Alcohol; увімкнути «Інші»; Шукати</x:v>
+        <x:v>ADMIN send з TSUK до зовнішньої location; GET UI states</x:v>
       </x:c>
       <x:c r="D69" t="str">
-        <x:v>Дані завантажені</x:v>
+        <x:v>рядок і sum&gt;0</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" t="str">
-        <x:v>TC-UI-RVW-002</x:v>
+        <x:v>TC-RVW-API-015</x:v>
       </x:c>
       <x:c r="B70" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C70" t="str">
-        <x:v>Перевірити «Сумарно переміщено»</x:v>
+        <x:v>GET states=CANCELLED|RETURNED</x:v>
       </x:c>
       <x:c r="D70" t="str">
-        <x:v>amount ≈ API sum</x:v>
+        <x:v>немає relocationId</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" t="str">
-        <x:v>TC-UI-RVW-002</x:v>
+        <x:v>TC-RVW-API-015</x:v>
       </x:c>
       <x:c r="B71" t="str">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C71" t="str">
-        <x:v>Перевірити таблицю</x:v>
+        <x:v>(опц.) RETURNED; GET UI states + end bust-cache</x:v>
       </x:c>
       <x:c r="D71" t="str">
-        <x:v>є product і ingredient рядки для Alcohol</x:v>
+        <x:v>немає рядка; sum≈0</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" t="str">
-        <x:v>TC-RVW-BOM-035</x:v>
+        <x:v>TC-RVW-API-016</x:v>
       </x:c>
       <x:c r="B72" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C72" t="str">
-        <x:v>Створити inventory stock Product і перемістити його до появи tech map</x:v>
+        <x:v>ADMIN send на типовий UNIT</x:v>
       </x:c>
       <x:c r="D72" t="str">
         <x:v>relocationId</x:v>
@@ -3952,86 +4328,422 @@
     </x:row>
     <x:row r="73">
       <x:c r="A73" t="str">
-        <x:v>TC-RVW-BOM-035</x:v>
+        <x:v>TC-RVW-API-016</x:v>
       </x:c>
       <x:c r="B73" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C73" t="str">
-        <x:v>Після переміщення створити tech map Product←Component</x:v>
+        <x:v>GET unitsOther=Інші</x:v>
       </x:c>
       <x:c r="D73" t="str">
-        <x:v>Tech map створена пізніше</x:v>
+        <x:v>є relocation; sum=amount</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" t="str">
-        <x:v>TC-RVW-BOM-035</x:v>
+        <x:v>TC-RVW-API-016</x:v>
       </x:c>
       <x:c r="B74" t="str">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C74" t="str">
-        <x:v>GET journal/sum</x:v>
+        <x:v>GET unit414Pm / unitSbsExcept414Pm</x:v>
       </x:c>
       <x:c r="D74" t="str">
-        <x:v>Component відсутній; Product лишається атомарним, isProduct=false</x:v>
+        <x:v>немає relocation</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" t="str">
-        <x:v>TC-RVW-BOM-036</x:v>
+        <x:v>TC-RVW-API-017</x:v>
       </x:c>
       <x:c r="B75" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C75" t="str">
-        <x:v>Отримати Product зовнішньою партією та перемістити її до появи tech map</x:v>
+        <x:v>Send на UNIT∈Інші</x:v>
       </x:c>
       <x:c r="D75" t="str">
-        <x:v>relocationId; isProduced=false</x:v>
+        <x:v>setup</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" t="str">
-        <x:v>TC-RVW-BOM-036</x:v>
+        <x:v>TC-RVW-API-017</x:v>
       </x:c>
       <x:c r="B76" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C76" t="str">
-        <x:v>Після переміщення створити tech map Product←Component</x:v>
+        <x:v>GET receiverIds+unit414Pm</x:v>
       </x:c>
       <x:c r="D76" t="str">
-        <x:v>Tech map створена пізніше</x:v>
+        <x:v>content=[]; sum=0</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" t="str">
-        <x:v>TC-RVW-BOM-036</x:v>
+        <x:v>TC-RVW-API-018</x:v>
       </x:c>
       <x:c r="B77" t="str">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C77" t="str">
-        <x:v>GET journal/sum за Component</x:v>
+        <x:v>Створити продукт A з компонентом Б; обидва ресурси віднести до категорії «Взуття»</x:v>
       </x:c>
       <x:c r="D77" t="str">
-        <x:v>Relocation відсутній; Component amount=0</x:v>
+        <x:v>Продукт A, компонент Б і спільна категорія створені</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" t="str">
-        <x:v>TC-RVW-BOM-036</x:v>
+        <x:v>TC-RVW-API-018</x:v>
       </x:c>
       <x:c r="B78" t="str">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C78" t="str">
-        <x:v>GET journal за Product</x:v>
+        <x:v>Виробити продукт A та передати його до вибраного підрозділу</x:v>
       </x:c>
       <x:c r="D78" t="str">
-        <x:v>Один атомарний рядок Product, isProduct=false</x:v>
+        <x:v>Створено одне фізичне переміщення продукту A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" t="str">
+        <x:v>TC-RVW-API-018</x:v>
+      </x:c>
+      <x:c r="B79" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C79" t="str">
+        <x:v>Виконати пошук Resource Viewer за категорією «Взуття» та одержувачем</x:v>
+      </x:c>
+      <x:c r="D79" t="str">
+        <x:v>relocationId присутній один раз; компонент Б має groupedFrom=[продукт A]</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" t="str">
+        <x:v>TC-RVW-API-019</x:v>
+      </x:c>
+      <x:c r="B80" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C80" t="str">
+        <x:v>Створити A з компонентом Б, виробити A та передати його</x:v>
+      </x:c>
+      <x:c r="D80" t="str">
+        <x:v>Один relocation готового виробу A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" t="str">
+        <x:v>TC-RVW-API-019</x:v>
+      </x:c>
+      <x:c r="B81" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C81" t="str">
+        <x:v>GET journal з resourceIds=[A,Б] та receiverIds</x:v>
+      </x:c>
+      <x:c r="D81" t="str">
+        <x:v>Для relocation є product-row з Б і self-row A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" t="str">
+        <x:v>TC-RVW-API-019</x:v>
+      </x:c>
+      <x:c r="B82" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C82" t="str">
+        <x:v>Перевірити sums і groupedFrom</x:v>
+      </x:c>
+      <x:c r="D82" t="str">
+        <x:v>A та Б присутні з коректними сумами; groupedFrom порожній</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" t="str">
+        <x:v>TC-RVW-API-021</x:v>
+      </x:c>
+      <x:c r="B83" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C83" t="str">
+        <x:v>Створити A з компонентом Б в одній категорії та передати A</x:v>
+      </x:c>
+      <x:c r="D83" t="str">
+        <x:v>Один relocation A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" t="str">
+        <x:v>TC-RVW-API-021</x:v>
+      </x:c>
+      <x:c r="B84" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C84" t="str">
+        <x:v>GET за categoryIds з groupByLowestComponents=false</x:v>
+      </x:c>
+      <x:c r="D84" t="str">
+        <x:v>Один self-row A; groupedFrom містить Б</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" t="str">
+        <x:v>TC-RVW-API-021</x:v>
+      </x:c>
+      <x:c r="B85" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C85" t="str">
+        <x:v>Перевірити sums</x:v>
+      </x:c>
+      <x:c r="D85" t="str">
+        <x:v>Є A з кількістю relocation; Б окремо відсутній</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" t="str">
+        <x:v>TC-RVW-API-020</x:v>
+      </x:c>
+      <x:c r="B86" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C86" t="str">
+        <x:v>GET /resources-viewer/export з resourceIds+receiverIds</x:v>
+      </x:c>
+      <x:c r="D86" t="str">
+        <x:v>200; Content-Disposition .xlsx; body&gt;0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" t="str">
+        <x:v>TC-RVW-API-020</x:v>
+      </x:c>
+      <x:c r="B87" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C87" t="str">
+        <x:v>GET export без tracking</x:v>
+      </x:c>
+      <x:c r="D87" t="str">
+        <x:v>200; body порожній</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" t="str">
+        <x:v>TC-UI-RES-AC-001</x:v>
+      </x:c>
+      <x:c r="B88" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C88" t="str">
+        <x:v>Відкрити /resources-viewer/relocation</x:v>
+      </x:c>
+      <x:c r="D88" t="str">
+        <x:v>Сторінка завантажена</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" t="str">
+        <x:v>TC-UI-RES-AC-001</x:v>
+      </x:c>
+      <x:c r="B89" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C89" t="str">
+        <x:v>Обрати категорію A; пошук ресурсів</x:v>
+      </x:c>
+      <x:c r="D89" t="str">
+        <x:v>є A; немає B</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" t="str">
+        <x:v>TC-UI-RES-AC-001</x:v>
+      </x:c>
+      <x:c r="B90" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C90" t="str">
+        <x:v>Очистити; пошук знову</x:v>
+      </x:c>
+      <x:c r="D90" t="str">
+        <x:v>є A і B</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" t="str">
+        <x:v>TC-UI-RVW-001</x:v>
+      </x:c>
+      <x:c r="B91" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C91" t="str">
+        <x:v>Увійти як динамічний Resource Viewer</x:v>
+      </x:c>
+      <x:c r="D91" t="str">
+        <x:v>SPA завантажено</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" t="str">
+        <x:v>TC-UI-RVW-001</x:v>
+      </x:c>
+      <x:c r="B92" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C92" t="str">
+        <x:v>Перевірити sidebar: «Відстеження ресурсів» видимий</x:v>
+      </x:c>
+      <x:c r="D92" t="str">
+        <x:v>link visible</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" t="str">
+        <x:v>TC-UI-RVW-001</x:v>
+      </x:c>
+      <x:c r="B93" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C93" t="str">
+        <x:v>Відкрити /resources-viewer/relocation</x:v>
+      </x:c>
+      <x:c r="D93" t="str">
+        <x:v>h1 «Журнал переміщень ресурсів»</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" t="str">
+        <x:v>TC-UI-RVW-002</x:v>
+      </x:c>
+      <x:c r="B94" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C94" t="str">
+        <x:v>Відкрити viewer; обрати Alcohol і конкретного зовнішнього отримувача; Шукати</x:v>
+      </x:c>
+      <x:c r="D94" t="str">
+        <x:v>Дані завантажені</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" t="str">
+        <x:v>TC-UI-RVW-002</x:v>
+      </x:c>
+      <x:c r="B95" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C95" t="str">
+        <x:v>Перевірити «Сумарно переміщено»</x:v>
+      </x:c>
+      <x:c r="D95" t="str">
+        <x:v>amount ≈ API sum</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" t="str">
+        <x:v>TC-UI-RVW-002</x:v>
+      </x:c>
+      <x:c r="B96" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C96" t="str">
+        <x:v>Перевірити таблицю</x:v>
+      </x:c>
+      <x:c r="D96" t="str">
+        <x:v>є product і ingredient рядки для Alcohol</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" t="str">
+        <x:v>TC-UI-RVW-003</x:v>
+      </x:c>
+      <x:c r="B97" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C97" t="str">
+        <x:v>Виконати пошук за ресурсом і одержувачем</x:v>
+      </x:c>
+      <x:c r="D97" t="str">
+        <x:v>Таблиця завантажена</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" t="str">
+        <x:v>TC-UI-RVW-003</x:v>
+      </x:c>
+      <x:c r="B98" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C98" t="str">
+        <x:v>Натиснути «Експорт в Excel»</x:v>
+      </x:c>
+      <x:c r="D98" t="str">
+        <x:v>Завантажено непорожній .xlsx</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="str">
+        <x:v>TC-UI-RVW-004</x:v>
+      </x:c>
+      <x:c r="B99" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C99" t="str">
+        <x:v>Обрати категорію продукту A і компонента Б</x:v>
+      </x:c>
+      <x:c r="D99" t="str">
+        <x:v>Перемикач grouping enabled і checked</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" t="str">
+        <x:v>TC-UI-RVW-004</x:v>
+      </x:c>
+      <x:c r="B100" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C100" t="str">
+        <x:v>Обрати одержувача та виконати пошук</x:v>
+      </x:c>
+      <x:c r="D100" t="str">
+        <x:v>Один рядок A; є Б і «Згруповано»</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" t="str">
+        <x:v>TC-UI-RVW-005</x:v>
+      </x:c>
+      <x:c r="B101" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C101" t="str">
+        <x:v>Явно вибрати готовий виріб A і компонент Б</x:v>
+      </x:c>
+      <x:c r="D101" t="str">
+        <x:v>Перемикач grouping disabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" t="str">
+        <x:v>TC-UI-RVW-005</x:v>
+      </x:c>
+      <x:c r="B102" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C102" t="str">
+        <x:v>Обрати одержувача та виконати пошук</x:v>
+      </x:c>
+      <x:c r="D102" t="str">
+        <x:v>Два логічні рядки relocation; немає «Згруповано»</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4044,35 +4756,23 @@
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">testId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">fieldKey</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">fieldLabel</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">fieldType</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">required</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">sortOrder</x:t>
-        </x:is>
+      <x:c r="A1" t="str">
+        <x:v>testId</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>fieldKey</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>fieldLabel</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>fieldType</x:v>
+      </x:c>
+      <x:c r="E1" t="str">
+        <x:v>required</x:v>
+      </x:c>
+      <x:c r="F1" t="str">
+        <x:v>sortOrder</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4085,25 +4785,17 @@
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">testId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">setName</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">active</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">valuesJson</x:t>
-        </x:is>
+      <x:c r="A1" t="str">
+        <x:v>testId</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>setName</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>active</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>valuesJson</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4116,36 +4808,28 @@
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">testId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">layer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">automationTestId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">sortOrder</x:t>
-        </x:is>
+      <x:c r="A1" t="str">
+        <x:v>testId</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>layer</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>automationTestId</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>sortOrder</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
-        <x:v>TC-RVW-BOM-001</x:v>
+        <x:v>TC-RVW-BOM-037</x:v>
       </x:c>
       <x:c r="B2" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>TC-RVW-BOM-001</x:v>
+        <x:v>TC-RVW-BOM-037</x:v>
       </x:c>
       <x:c r="D2" t="str">
         <x:v>0</x:v>
@@ -4153,13 +4837,13 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
-        <x:v>TC-RVW-BOM-002</x:v>
+        <x:v>TC-RVW-BOM-001</x:v>
       </x:c>
       <x:c r="B3" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>TC-RVW-BOM-002</x:v>
+        <x:v>TC-RVW-BOM-001</x:v>
       </x:c>
       <x:c r="D3" t="str">
         <x:v>0</x:v>
@@ -4167,13 +4851,13 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
-        <x:v>TC-RVW-BOM-003</x:v>
+        <x:v>TC-RVW-BOM-002</x:v>
       </x:c>
       <x:c r="B4" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>TC-RVW-BOM-003</x:v>
+        <x:v>TC-RVW-BOM-002</x:v>
       </x:c>
       <x:c r="D4" t="str">
         <x:v>0</x:v>
@@ -4181,13 +4865,13 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
-        <x:v>TC-RVW-BOM-004</x:v>
+        <x:v>TC-RVW-BOM-003</x:v>
       </x:c>
       <x:c r="B5" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>TC-RVW-BOM-004</x:v>
+        <x:v>TC-RVW-BOM-003</x:v>
       </x:c>
       <x:c r="D5" t="str">
         <x:v>0</x:v>
@@ -4195,13 +4879,13 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str">
-        <x:v>TC-RVW-BOM-010</x:v>
+        <x:v>TC-RVW-BOM-004</x:v>
       </x:c>
       <x:c r="B6" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C6" t="str">
-        <x:v>TC-RVW-BOM-010</x:v>
+        <x:v>TC-RVW-BOM-004</x:v>
       </x:c>
       <x:c r="D6" t="str">
         <x:v>0</x:v>
@@ -4209,13 +4893,13 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
-        <x:v>TC-RVW-BOM-011</x:v>
+        <x:v>TC-RVW-BOM-010</x:v>
       </x:c>
       <x:c r="B7" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C7" t="str">
-        <x:v>TC-RVW-BOM-011</x:v>
+        <x:v>TC-RVW-BOM-010</x:v>
       </x:c>
       <x:c r="D7" t="str">
         <x:v>0</x:v>
@@ -4223,13 +4907,13 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str">
-        <x:v>TC-RVW-BOM-012</x:v>
+        <x:v>TC-RVW-BOM-011</x:v>
       </x:c>
       <x:c r="B8" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C8" t="str">
-        <x:v>TC-RVW-BOM-012</x:v>
+        <x:v>TC-RVW-BOM-011</x:v>
       </x:c>
       <x:c r="D8" t="str">
         <x:v>0</x:v>
@@ -4237,13 +4921,13 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="str">
-        <x:v>TC-RVW-BOM-020</x:v>
+        <x:v>TC-RVW-BOM-012</x:v>
       </x:c>
       <x:c r="B9" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C9" t="str">
-        <x:v>TC-RVW-BOM-020</x:v>
+        <x:v>TC-RVW-BOM-012</x:v>
       </x:c>
       <x:c r="D9" t="str">
         <x:v>0</x:v>
@@ -4251,13 +4935,13 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="str">
-        <x:v>TC-RVW-BOM-021</x:v>
+        <x:v>TC-RVW-BOM-020</x:v>
       </x:c>
       <x:c r="B10" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C10" t="str">
-        <x:v>TC-RVW-BOM-021</x:v>
+        <x:v>TC-RVW-BOM-020</x:v>
       </x:c>
       <x:c r="D10" t="str">
         <x:v>0</x:v>
@@ -4265,13 +4949,13 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="str">
-        <x:v>TC-RVW-BOM-022</x:v>
+        <x:v>TC-RVW-BOM-021</x:v>
       </x:c>
       <x:c r="B11" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C11" t="str">
-        <x:v>TC-RVW-BOM-022</x:v>
+        <x:v>TC-RVW-BOM-021</x:v>
       </x:c>
       <x:c r="D11" t="str">
         <x:v>0</x:v>
@@ -4279,13 +4963,13 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="str">
-        <x:v>TC-RVW-ALT-001</x:v>
+        <x:v>TC-RVW-BOM-022</x:v>
       </x:c>
       <x:c r="B12" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C12" t="str">
-        <x:v>TC-RVW-ALT-001</x:v>
+        <x:v>TC-RVW-BOM-022</x:v>
       </x:c>
       <x:c r="D12" t="str">
         <x:v>0</x:v>
@@ -4293,13 +4977,13 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
-        <x:v>TC-RVW-ALT-002</x:v>
+        <x:v>TC-RVW-ALT-001</x:v>
       </x:c>
       <x:c r="B13" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C13" t="str">
-        <x:v>TC-RVW-ALT-002</x:v>
+        <x:v>TC-RVW-ALT-001</x:v>
       </x:c>
       <x:c r="D13" t="str">
         <x:v>0</x:v>
@@ -4307,13 +4991,13 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
-        <x:v>TC-RVW-BOM-030</x:v>
+        <x:v>TC-RVW-ALT-002</x:v>
       </x:c>
       <x:c r="B14" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C14" t="str">
-        <x:v>TC-RVW-BOM-030</x:v>
+        <x:v>TC-RVW-ALT-002</x:v>
       </x:c>
       <x:c r="D14" t="str">
         <x:v>0</x:v>
@@ -4321,13 +5005,13 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
-        <x:v>TC-RVW-BOM-031</x:v>
+        <x:v>TC-RVW-BOM-030</x:v>
       </x:c>
       <x:c r="B15" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C15" t="str">
-        <x:v>TC-RVW-BOM-031</x:v>
+        <x:v>TC-RVW-BOM-030</x:v>
       </x:c>
       <x:c r="D15" t="str">
         <x:v>0</x:v>
@@ -4335,13 +5019,13 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
-        <x:v>TC-RVW-BOM-032</x:v>
+        <x:v>TC-RVW-BOM-031</x:v>
       </x:c>
       <x:c r="B16" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C16" t="str">
-        <x:v>TC-RVW-BOM-032</x:v>
+        <x:v>TC-RVW-BOM-031</x:v>
       </x:c>
       <x:c r="D16" t="str">
         <x:v>0</x:v>
@@ -4349,13 +5033,13 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
-        <x:v>TC-RVW-BOM-033</x:v>
+        <x:v>TC-RVW-BOM-032</x:v>
       </x:c>
       <x:c r="B17" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C17" t="str">
-        <x:v>TC-RVW-BOM-033</x:v>
+        <x:v>TC-RVW-BOM-032</x:v>
       </x:c>
       <x:c r="D17" t="str">
         <x:v>0</x:v>
@@ -4363,13 +5047,13 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
-        <x:v>TC-RVW-BOM-034</x:v>
+        <x:v>TC-RVW-BOM-033</x:v>
       </x:c>
       <x:c r="B18" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C18" t="str">
-        <x:v>TC-RVW-BOM-034</x:v>
+        <x:v>TC-RVW-BOM-033</x:v>
       </x:c>
       <x:c r="D18" t="str">
         <x:v>0</x:v>
@@ -4377,13 +5061,13 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="str">
-        <x:v>TC-RVW-001</x:v>
+        <x:v>TC-RVW-BOM-034</x:v>
       </x:c>
       <x:c r="B19" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C19" t="str">
-        <x:v>TC-RVW-001</x:v>
+        <x:v>TC-RVW-BOM-034</x:v>
       </x:c>
       <x:c r="D19" t="str">
         <x:v>0</x:v>
@@ -4391,13 +5075,13 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="str">
-        <x:v>TC-RVW-API-001</x:v>
+        <x:v>TC-RVW-BOM-035</x:v>
       </x:c>
       <x:c r="B20" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C20" t="str">
-        <x:v>TC-RVW-API-001</x:v>
+        <x:v>TC-RVW-BOM-035</x:v>
       </x:c>
       <x:c r="D20" t="str">
         <x:v>0</x:v>
@@ -4405,13 +5089,13 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="str">
-        <x:v>TC-RVW-API-002</x:v>
+        <x:v>TC-RVW-BOM-036</x:v>
       </x:c>
       <x:c r="B21" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C21" t="str">
-        <x:v>TC-RVW-API-002</x:v>
+        <x:v>TC-RVW-BOM-036</x:v>
       </x:c>
       <x:c r="D21" t="str">
         <x:v>0</x:v>
@@ -4419,13 +5103,13 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
-        <x:v>TC-RVW-API-003</x:v>
+        <x:v>TC-RVW-001</x:v>
       </x:c>
       <x:c r="B22" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>TC-RVW-API-003</x:v>
+        <x:v>TC-RVW-001</x:v>
       </x:c>
       <x:c r="D22" t="str">
         <x:v>0</x:v>
@@ -4433,13 +5117,13 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
-        <x:v>TC-RVW-API-010</x:v>
+        <x:v>TC-RVW-API-001</x:v>
       </x:c>
       <x:c r="B23" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C23" t="str">
-        <x:v>TC-RVW-API-010</x:v>
+        <x:v>TC-RVW-API-001</x:v>
       </x:c>
       <x:c r="D23" t="str">
         <x:v>0</x:v>
@@ -4447,13 +5131,13 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str">
-        <x:v>TC-RVW-API-011</x:v>
+        <x:v>TC-RVW-API-002</x:v>
       </x:c>
       <x:c r="B24" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C24" t="str">
-        <x:v>TC-RVW-API-011</x:v>
+        <x:v>TC-RVW-API-002</x:v>
       </x:c>
       <x:c r="D24" t="str">
         <x:v>0</x:v>
@@ -4461,13 +5145,13 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="str">
-        <x:v>TC-RVW-API-012</x:v>
+        <x:v>TC-RVW-API-003</x:v>
       </x:c>
       <x:c r="B25" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C25" t="str">
-        <x:v>TC-RVW-API-012</x:v>
+        <x:v>TC-RVW-API-003</x:v>
       </x:c>
       <x:c r="D25" t="str">
         <x:v>0</x:v>
@@ -4475,13 +5159,13 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str">
-        <x:v>TC-RVW-API-013</x:v>
+        <x:v>TC-RVW-API-022</x:v>
       </x:c>
       <x:c r="B26" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>TC-RVW-API-013</x:v>
+        <x:v>TC-RVW-API-022</x:v>
       </x:c>
       <x:c r="D26" t="str">
         <x:v>0</x:v>
@@ -4489,13 +5173,13 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="str">
-        <x:v>TC-RVW-API-014</x:v>
+        <x:v>TC-RVW-API-023</x:v>
       </x:c>
       <x:c r="B27" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>TC-RVW-API-014</x:v>
+        <x:v>TC-RVW-API-023</x:v>
       </x:c>
       <x:c r="D27" t="str">
         <x:v>0</x:v>
@@ -4503,13 +5187,13 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="str">
-        <x:v>TC-RVW-API-015</x:v>
+        <x:v>TC-RVW-API-010</x:v>
       </x:c>
       <x:c r="B28" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>TC-RVW-API-015</x:v>
+        <x:v>TC-RVW-API-010</x:v>
       </x:c>
       <x:c r="D28" t="str">
         <x:v>0</x:v>
@@ -4517,13 +5201,13 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="str">
-        <x:v>TC-RVW-API-016</x:v>
+        <x:v>TC-RVW-API-011</x:v>
       </x:c>
       <x:c r="B29" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>TC-RVW-API-016</x:v>
+        <x:v>TC-RVW-API-011</x:v>
       </x:c>
       <x:c r="D29" t="str">
         <x:v>0</x:v>
@@ -4531,13 +5215,13 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
-        <x:v>TC-RVW-API-017</x:v>
+        <x:v>TC-RVW-API-012</x:v>
       </x:c>
       <x:c r="B30" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>TC-RVW-API-017</x:v>
+        <x:v>TC-RVW-API-012</x:v>
       </x:c>
       <x:c r="D30" t="str">
         <x:v>0</x:v>
@@ -4545,13 +5229,13 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str">
-        <x:v>TC-RVW-API-018</x:v>
+        <x:v>TC-RVW-API-013</x:v>
       </x:c>
       <x:c r="B31" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C31" t="str">
-        <x:v>TC-RVW-API-018</x:v>
+        <x:v>TC-RVW-API-013</x:v>
       </x:c>
       <x:c r="D31" t="str">
         <x:v>0</x:v>
@@ -4559,13 +5243,13 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="str">
-        <x:v>TC-RVW-API-020</x:v>
+        <x:v>TC-RVW-API-014</x:v>
       </x:c>
       <x:c r="B32" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C32" t="str">
-        <x:v>TC-RVW-API-020</x:v>
+        <x:v>TC-RVW-API-014</x:v>
       </x:c>
       <x:c r="D32" t="str">
         <x:v>0</x:v>
@@ -4573,13 +5257,13 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="str">
-        <x:v>TC-UI-RES-AC-001</x:v>
+        <x:v>TC-RVW-API-015</x:v>
       </x:c>
       <x:c r="B33" t="str">
-        <x:v>UI</x:v>
+        <x:v>API</x:v>
       </x:c>
       <x:c r="C33" t="str">
-        <x:v>TC-UI-RES-AC-001</x:v>
+        <x:v>TC-RVW-API-015</x:v>
       </x:c>
       <x:c r="D33" t="str">
         <x:v>0</x:v>
@@ -4587,13 +5271,13 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="str">
-        <x:v>TC-UI-RVW-001</x:v>
+        <x:v>TC-RVW-API-016</x:v>
       </x:c>
       <x:c r="B34" t="str">
-        <x:v>UI</x:v>
+        <x:v>API</x:v>
       </x:c>
       <x:c r="C34" t="str">
-        <x:v>TC-UI-RVW-001</x:v>
+        <x:v>TC-RVW-API-016</x:v>
       </x:c>
       <x:c r="D34" t="str">
         <x:v>0</x:v>
@@ -4601,13 +5285,13 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="str">
-        <x:v>TC-UI-RVW-002</x:v>
+        <x:v>TC-RVW-API-017</x:v>
       </x:c>
       <x:c r="B35" t="str">
-        <x:v>UI</x:v>
+        <x:v>API</x:v>
       </x:c>
       <x:c r="C35" t="str">
-        <x:v>TC-UI-RVW-002</x:v>
+        <x:v>TC-RVW-API-017</x:v>
       </x:c>
       <x:c r="D35" t="str">
         <x:v>0</x:v>
@@ -4615,13 +5299,13 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="str">
-        <x:v>TC-RVW-BOM-035</x:v>
+        <x:v>TC-RVW-API-018</x:v>
       </x:c>
       <x:c r="B36" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C36" t="str">
-        <x:v>TC-RVW-BOM-035</x:v>
+        <x:v>TC-RVW-API-018</x:v>
       </x:c>
       <x:c r="D36" t="str">
         <x:v>0</x:v>
@@ -4629,15 +5313,127 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="str">
-        <x:v>TC-RVW-BOM-036</x:v>
+        <x:v>TC-RVW-API-019</x:v>
       </x:c>
       <x:c r="B37" t="str">
         <x:v>API</x:v>
       </x:c>
       <x:c r="C37" t="str">
-        <x:v>TC-RVW-BOM-036</x:v>
+        <x:v>TC-RVW-API-019</x:v>
       </x:c>
       <x:c r="D37" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>TC-RVW-API-021</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>API</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>TC-RVW-API-021</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>TC-RVW-API-020</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>API</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>TC-RVW-API-020</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>TC-UI-RES-AC-001</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>UI</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>TC-UI-RES-AC-001</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>TC-UI-RVW-001</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>UI</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>TC-UI-RVW-001</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>TC-UI-RVW-002</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>UI</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>TC-UI-RVW-002</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>TC-UI-RVW-003</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>UI</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>TC-UI-RVW-003</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>TC-UI-RVW-004</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>UI</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>TC-UI-RVW-004</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>TC-UI-RVW-005</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>UI</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>TC-UI-RVW-005</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -4651,20 +5447,16 @@
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">testId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">crossFeatureSlug</x:t>
-        </x:is>
+      <x:c r="A1" t="str">
+        <x:v>testId</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>crossFeatureSlug</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
-        <x:v>TC-RVW-BOM-001</x:v>
+        <x:v>TC-RVW-BOM-037</x:v>
       </x:c>
       <x:c r="B2" t="str">
         <x:v>resource-viewer</x:v>
@@ -4672,7 +5464,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
-        <x:v>TC-RVW-BOM-002</x:v>
+        <x:v>TC-RVW-BOM-001</x:v>
       </x:c>
       <x:c r="B3" t="str">
         <x:v>resource-viewer</x:v>
@@ -4680,7 +5472,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
-        <x:v>TC-RVW-BOM-003</x:v>
+        <x:v>TC-RVW-BOM-002</x:v>
       </x:c>
       <x:c r="B4" t="str">
         <x:v>resource-viewer</x:v>
@@ -4688,7 +5480,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
-        <x:v>TC-RVW-BOM-004</x:v>
+        <x:v>TC-RVW-BOM-003</x:v>
       </x:c>
       <x:c r="B5" t="str">
         <x:v>resource-viewer</x:v>
@@ -4696,7 +5488,7 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str">
-        <x:v>TC-RVW-BOM-010</x:v>
+        <x:v>TC-RVW-BOM-004</x:v>
       </x:c>
       <x:c r="B6" t="str">
         <x:v>resource-viewer</x:v>
@@ -4704,7 +5496,7 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
-        <x:v>TC-RVW-BOM-011</x:v>
+        <x:v>TC-RVW-BOM-010</x:v>
       </x:c>
       <x:c r="B7" t="str">
         <x:v>resource-viewer</x:v>
@@ -4712,7 +5504,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str">
-        <x:v>TC-RVW-BOM-012</x:v>
+        <x:v>TC-RVW-BOM-011</x:v>
       </x:c>
       <x:c r="B8" t="str">
         <x:v>resource-viewer</x:v>
@@ -4720,7 +5512,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="str">
-        <x:v>TC-RVW-BOM-020</x:v>
+        <x:v>TC-RVW-BOM-012</x:v>
       </x:c>
       <x:c r="B9" t="str">
         <x:v>resource-viewer</x:v>
@@ -4728,7 +5520,7 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="str">
-        <x:v>TC-RVW-BOM-021</x:v>
+        <x:v>TC-RVW-BOM-020</x:v>
       </x:c>
       <x:c r="B10" t="str">
         <x:v>resource-viewer</x:v>
@@ -4736,7 +5528,7 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="str">
-        <x:v>TC-RVW-BOM-022</x:v>
+        <x:v>TC-RVW-BOM-021</x:v>
       </x:c>
       <x:c r="B11" t="str">
         <x:v>resource-viewer</x:v>
@@ -4744,7 +5536,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="str">
-        <x:v>TC-RVW-ALT-001</x:v>
+        <x:v>TC-RVW-BOM-022</x:v>
       </x:c>
       <x:c r="B12" t="str">
         <x:v>resource-viewer</x:v>
@@ -4752,7 +5544,7 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
-        <x:v>TC-RVW-ALT-002</x:v>
+        <x:v>TC-RVW-ALT-001</x:v>
       </x:c>
       <x:c r="B13" t="str">
         <x:v>resource-viewer</x:v>
@@ -4760,7 +5552,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
-        <x:v>TC-RVW-BOM-030</x:v>
+        <x:v>TC-RVW-ALT-002</x:v>
       </x:c>
       <x:c r="B14" t="str">
         <x:v>resource-viewer</x:v>
@@ -4768,7 +5560,7 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
-        <x:v>TC-RVW-BOM-031</x:v>
+        <x:v>TC-RVW-BOM-030</x:v>
       </x:c>
       <x:c r="B15" t="str">
         <x:v>resource-viewer</x:v>
@@ -4776,7 +5568,7 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
-        <x:v>TC-RVW-BOM-032</x:v>
+        <x:v>TC-RVW-BOM-031</x:v>
       </x:c>
       <x:c r="B16" t="str">
         <x:v>resource-viewer</x:v>
@@ -4784,7 +5576,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
-        <x:v>TC-RVW-BOM-033</x:v>
+        <x:v>TC-RVW-BOM-032</x:v>
       </x:c>
       <x:c r="B17" t="str">
         <x:v>resource-viewer</x:v>
@@ -4792,7 +5584,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
-        <x:v>TC-RVW-BOM-034</x:v>
+        <x:v>TC-RVW-BOM-033</x:v>
       </x:c>
       <x:c r="B18" t="str">
         <x:v>resource-viewer</x:v>
@@ -4800,7 +5592,7 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="str">
-        <x:v>TC-RVW-001</x:v>
+        <x:v>TC-RVW-BOM-034</x:v>
       </x:c>
       <x:c r="B19" t="str">
         <x:v>resource-viewer</x:v>
@@ -4808,7 +5600,7 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="str">
-        <x:v>TC-RVW-API-001</x:v>
+        <x:v>TC-RVW-BOM-035</x:v>
       </x:c>
       <x:c r="B20" t="str">
         <x:v>resource-viewer</x:v>
@@ -4816,7 +5608,7 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="str">
-        <x:v>TC-RVW-API-002</x:v>
+        <x:v>TC-RVW-BOM-036</x:v>
       </x:c>
       <x:c r="B21" t="str">
         <x:v>resource-viewer</x:v>
@@ -4824,7 +5616,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
-        <x:v>TC-RVW-API-003</x:v>
+        <x:v>TC-RVW-001</x:v>
       </x:c>
       <x:c r="B22" t="str">
         <x:v>resource-viewer</x:v>
@@ -4832,7 +5624,7 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
-        <x:v>TC-RVW-API-010</x:v>
+        <x:v>TC-RVW-API-001</x:v>
       </x:c>
       <x:c r="B23" t="str">
         <x:v>resource-viewer</x:v>
@@ -4840,7 +5632,7 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str">
-        <x:v>TC-RVW-API-011</x:v>
+        <x:v>TC-RVW-API-002</x:v>
       </x:c>
       <x:c r="B24" t="str">
         <x:v>resource-viewer</x:v>
@@ -4848,7 +5640,7 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="str">
-        <x:v>TC-RVW-API-012</x:v>
+        <x:v>TC-RVW-API-003</x:v>
       </x:c>
       <x:c r="B25" t="str">
         <x:v>resource-viewer</x:v>
@@ -4856,7 +5648,7 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str">
-        <x:v>TC-RVW-API-013</x:v>
+        <x:v>TC-RVW-API-022</x:v>
       </x:c>
       <x:c r="B26" t="str">
         <x:v>resource-viewer</x:v>
@@ -4864,7 +5656,7 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="str">
-        <x:v>TC-RVW-API-014</x:v>
+        <x:v>TC-RVW-API-023</x:v>
       </x:c>
       <x:c r="B27" t="str">
         <x:v>resource-viewer</x:v>
@@ -4872,7 +5664,7 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="str">
-        <x:v>TC-RVW-API-015</x:v>
+        <x:v>TC-RVW-API-010</x:v>
       </x:c>
       <x:c r="B28" t="str">
         <x:v>resource-viewer</x:v>
@@ -4880,7 +5672,7 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="str">
-        <x:v>TC-RVW-API-016</x:v>
+        <x:v>TC-RVW-API-011</x:v>
       </x:c>
       <x:c r="B29" t="str">
         <x:v>resource-viewer</x:v>
@@ -4888,7 +5680,7 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
-        <x:v>TC-RVW-API-017</x:v>
+        <x:v>TC-RVW-API-012</x:v>
       </x:c>
       <x:c r="B30" t="str">
         <x:v>resource-viewer</x:v>
@@ -4896,7 +5688,7 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str">
-        <x:v>TC-RVW-API-018</x:v>
+        <x:v>TC-RVW-API-013</x:v>
       </x:c>
       <x:c r="B31" t="str">
         <x:v>resource-viewer</x:v>
@@ -4904,7 +5696,7 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="str">
-        <x:v>TC-RVW-API-020</x:v>
+        <x:v>TC-RVW-API-014</x:v>
       </x:c>
       <x:c r="B32" t="str">
         <x:v>resource-viewer</x:v>
@@ -4912,7 +5704,7 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="str">
-        <x:v>TC-UI-RES-AC-001</x:v>
+        <x:v>TC-RVW-API-015</x:v>
       </x:c>
       <x:c r="B33" t="str">
         <x:v>resource-viewer</x:v>
@@ -4920,7 +5712,7 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="str">
-        <x:v>TC-UI-RVW-001</x:v>
+        <x:v>TC-RVW-API-016</x:v>
       </x:c>
       <x:c r="B34" t="str">
         <x:v>resource-viewer</x:v>
@@ -4928,7 +5720,7 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="str">
-        <x:v>TC-UI-RVW-002</x:v>
+        <x:v>TC-RVW-API-017</x:v>
       </x:c>
       <x:c r="B35" t="str">
         <x:v>resource-viewer</x:v>
@@ -4936,7 +5728,7 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="str">
-        <x:v>TC-RVW-BOM-035</x:v>
+        <x:v>TC-RVW-API-018</x:v>
       </x:c>
       <x:c r="B36" t="str">
         <x:v>resource-viewer</x:v>
@@ -4944,9 +5736,73 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="str">
-        <x:v>TC-RVW-BOM-036</x:v>
+        <x:v>TC-RVW-API-019</x:v>
       </x:c>
       <x:c r="B37" t="str">
+        <x:v>resource-viewer</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>TC-RVW-API-021</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>resource-viewer</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>TC-RVW-API-020</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>resource-viewer</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>TC-UI-RES-AC-001</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>resource-viewer</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>TC-UI-RVW-001</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>resource-viewer</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>TC-UI-RVW-002</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>resource-viewer</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>TC-UI-RVW-003</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>resource-viewer</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>TC-UI-RVW-004</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>resource-viewer</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>TC-UI-RVW-005</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
         <x:v>resource-viewer</x:v>
       </x:c>
     </x:row>
